--- a/dc-uat-checklist-updated.xlsx
+++ b/dc-uat-checklist-updated.xlsx
@@ -1,26 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\daycare-system\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AEAC74A-89F9-4C54-81C0-14457124E693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="UAT Checklist" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Instructions" sheetId="1" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" r:id="rId2"/>
+    <sheet name="UAT Checklist" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instructions!$A$1:$C$27</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Summary!$A$1:$I$28</definedName>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'UAT Checklist'!$A$1:$K$127</definedName>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">'UAT Checklist'!$1:$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'UAT Checklist'!$A$1:$K$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UAT Checklist'!$A$1:$K$127</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Instructions!$A$1:$C$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Summary!$A$1:$I$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'UAT Checklist'!$A$1:$K$127</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'UAT Checklist'!$1:$1</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -29,1770 +43,1772 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="569">
-  <si>
-    <t xml:space="preserve">Emagine U At Play — UAT Checklist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End-to-end User Acceptance Testing checklist for the daycare + therapy management system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How to use this workbook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the "UAT Checklist" tab. It lists every test case across all 22 modules, in build order.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Work through it top to bottom, or use the filter arrows on row 1 to test one module at a time.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. For each row: perform the Steps to Execute, compare the real result to Expected Result, then fill in Status, Actual Result / Comments, Tested By, and Date Tested.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Only edit the columns Status, Actual Result / Comments, Tested By, and Date Tested — every other column is the test spec itself and shouldn't be changed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Check the "Summary" tab any time for a live pass/fail count per module — it updates automatically from your Status entries.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status column legend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not Tested — default state, not yet attempted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pass — behaved exactly as Expected Result describes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fail — did not match Expected Result — describe what happened in Actual Result / Comments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blocked — could not be tested (e.g. a dependency isn't built yet)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/A — doesn't apply to your current setup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority column legend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High — core money, safety, or access-control behavior; test these first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medium — important day-to-day functionality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low — nice-to-have / cosmetic behavior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Before you start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Make sure the database has been freshly seeded (php artisan migrate:fresh --seed) so admin@daycare.com exists and role/permission data matches what these test cases assume.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Have at least one seeded parent account with a child, and one seeded staff account, so role-based test cases (marked across every module) have something real to check against.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UAT Progress Summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Updates automatically from the Status column on the UAT Checklist tab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Module</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Cases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not Tested</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blocked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pass Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Authentication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles &amp; Permissions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Children Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guardian-Child Access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enrollments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waitlist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attendance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Child Daily Logs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Documents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Activities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drop-in Bookings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billing - Daycare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Therapy Wing Setup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Therapy Sessions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Therapy Packages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Therapy Billing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Announcements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Child Safety QR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security &amp; Non-Functional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steps to Execute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected Result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actual Result / Comments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tested By</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date Tested</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTH-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parent self-registration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Go to /register
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="571">
+  <si>
+    <t>Emagine U At Play — UAT Checklist</t>
+  </si>
+  <si>
+    <t>End-to-end User Acceptance Testing checklist for the daycare + therapy management system</t>
+  </si>
+  <si>
+    <t>How to use this workbook</t>
+  </si>
+  <si>
+    <t>1. Open the "UAT Checklist" tab. It lists every test case across all 22 modules, in build order.</t>
+  </si>
+  <si>
+    <t>2. Work through it top to bottom, or use the filter arrows on row 1 to test one module at a time.</t>
+  </si>
+  <si>
+    <t>3. For each row: perform the Steps to Execute, compare the real result to Expected Result, then fill in Status, Actual Result / Comments, Tested By, and Date Tested.</t>
+  </si>
+  <si>
+    <t>4. Only edit the columns Status, Actual Result / Comments, Tested By, and Date Tested — every other column is the test spec itself and shouldn't be changed.</t>
+  </si>
+  <si>
+    <t>5. Check the "Summary" tab any time for a live pass/fail count per module — it updates automatically from your Status entries.</t>
+  </si>
+  <si>
+    <t>Status column legend</t>
+  </si>
+  <si>
+    <t>Not Tested — default state, not yet attempted</t>
+  </si>
+  <si>
+    <t>Pass — behaved exactly as Expected Result describes</t>
+  </si>
+  <si>
+    <t>Fail — did not match Expected Result — describe what happened in Actual Result / Comments</t>
+  </si>
+  <si>
+    <t>Blocked — could not be tested (e.g. a dependency isn't built yet)</t>
+  </si>
+  <si>
+    <t>N/A — doesn't apply to your current setup</t>
+  </si>
+  <si>
+    <t>Priority column legend</t>
+  </si>
+  <si>
+    <t>High — core money, safety, or access-control behavior; test these first</t>
+  </si>
+  <si>
+    <t>Medium — important day-to-day functionality</t>
+  </si>
+  <si>
+    <t>Low — nice-to-have / cosmetic behavior</t>
+  </si>
+  <si>
+    <t>Before you start</t>
+  </si>
+  <si>
+    <t>Make sure the database has been freshly seeded (php artisan migrate:fresh --seed) so admin@daycare.com exists and role/permission data matches what these test cases assume.</t>
+  </si>
+  <si>
+    <t>Have at least one seeded parent account with a child, and one seeded staff account, so role-based test cases (marked across every module) have something real to check against.</t>
+  </si>
+  <si>
+    <t>UAT Progress Summary</t>
+  </si>
+  <si>
+    <t>Updates automatically from the Status column on the UAT Checklist tab</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Total Cases</t>
+  </si>
+  <si>
+    <t>Not Tested</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Blocked</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Pass Rate</t>
+  </si>
+  <si>
+    <t>Authentication</t>
+  </si>
+  <si>
+    <t>User Management</t>
+  </si>
+  <si>
+    <t>Roles &amp; Permissions</t>
+  </si>
+  <si>
+    <t>Children Management</t>
+  </si>
+  <si>
+    <t>Guardian-Child Access</t>
+  </si>
+  <si>
+    <t>Programs</t>
+  </si>
+  <si>
+    <t>Enrollments</t>
+  </si>
+  <si>
+    <t>Waitlist</t>
+  </si>
+  <si>
+    <t>Attendance</t>
+  </si>
+  <si>
+    <t>Child Daily Logs</t>
+  </si>
+  <si>
+    <t>Documents</t>
+  </si>
+  <si>
+    <t>Activities</t>
+  </si>
+  <si>
+    <t>Drop-in Bookings</t>
+  </si>
+  <si>
+    <t>Billing - Daycare</t>
+  </si>
+  <si>
+    <t>Therapy Wing Setup</t>
+  </si>
+  <si>
+    <t>Therapy Sessions</t>
+  </si>
+  <si>
+    <t>Therapy Packages</t>
+  </si>
+  <si>
+    <t>Therapy Billing</t>
+  </si>
+  <si>
+    <t>Reports</t>
+  </si>
+  <si>
+    <t>Announcements</t>
+  </si>
+  <si>
+    <t>Child Safety QR</t>
+  </si>
+  <si>
+    <t>Security &amp; Non-Functional</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Test ID</t>
+  </si>
+  <si>
+    <t>Test Scenario</t>
+  </si>
+  <si>
+    <t>Steps to Execute</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Actual Result / Comments</t>
+  </si>
+  <si>
+    <t>Tested By</t>
+  </si>
+  <si>
+    <t>Date Tested</t>
+  </si>
+  <si>
+    <t>AUTH-01</t>
+  </si>
+  <si>
+    <t>Parent self-registration</t>
+  </si>
+  <si>
+    <t>1. Go to /register
 2. Select role = Parent
 3. Fill first/last name, email, phone, password
 4. Submit</t>
   </si>
   <si>
-    <t xml:space="preserve">New user created with role=parent; matching parents profile row created; user auto-logged in and redirected to dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTH-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff self-registration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Go to /register
+    <t>New user created with role=parent; matching parents profile row created; user auto-logged in and redirected to dashboard</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>AUTH-02</t>
+  </si>
+  <si>
+    <t>Staff self-registration</t>
+  </si>
+  <si>
+    <t>1. Go to /register
 2. Select role = Staff
 3. Fill required fields
 4. Submit</t>
   </si>
   <si>
-    <t xml:space="preserve">staff profile row created with default role=teacher; redirected to dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTH-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duplicate email registration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Register using an email already in the users table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation error shown: email already taken; no duplicate row created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTH-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Successful login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Go to /login
+    <t>staff profile row created with default role=teacher; redirected to dashboard</t>
+  </si>
+  <si>
+    <t>AUTH-03</t>
+  </si>
+  <si>
+    <t>Duplicate email registration</t>
+  </si>
+  <si>
+    <t>1. Register using an email already in the users table</t>
+  </si>
+  <si>
+    <t>Validation error shown: email already taken; no duplicate row created</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>AUTH-04</t>
+  </si>
+  <si>
+    <t>Successful login</t>
+  </si>
+  <si>
+    <t>1. Go to /login
 2. Enter correct email/password
 3. Submit</t>
   </si>
   <si>
-    <t xml:space="preserve">Redirected to dashboard; last_login timestamp updated; session established</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTH-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Login with wrong password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enter correct email, incorrect password
+    <t>Redirected to dashboard; last_login timestamp updated; session established</t>
+  </si>
+  <si>
+    <t>AUTH-05</t>
+  </si>
+  <si>
+    <t>Login with wrong password</t>
+  </si>
+  <si>
+    <t>1. Enter correct email, incorrect password
 2. Submit</t>
   </si>
   <si>
-    <t xml:space="preserve">Error "credentials do not match" shown; rate limiter attempt count increases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTH-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Login lockout after repeated failures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Attempt login with wrong password 5 times within a minute
+    <t>Error "credentials do not match" shown; rate limiter attempt count increases</t>
+  </si>
+  <si>
+    <t>AUTH-06</t>
+  </si>
+  <si>
+    <t>Login lockout after repeated failures</t>
+  </si>
+  <si>
+    <t>1. Attempt login with wrong password 5 times within a minute
 2. Try a 6th time</t>
   </si>
   <si>
-    <t xml:space="preserve">Locked out with a "too many attempts, try again in X seconds" message</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTH-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deactivated account login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Admin sets a user's is_active = false
+    <t>Locked out with a "too many attempts, try again in X seconds" message</t>
+  </si>
+  <si>
+    <t>AUTH-07</t>
+  </si>
+  <si>
+    <t>Deactivated account login</t>
+  </si>
+  <si>
+    <t>1. Admin sets a user's is_active = false
 2. That user attempts to log in with correct credentials</t>
   </si>
   <si>
-    <t xml:space="preserve">Login is immediately reversed; "account deactivated" message shown; user is logged out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTH-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. While logged in, click Logout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Session invalidated and token regenerated; redirected to /login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTH-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forgot password request</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Go to /forgot-password
+    <t>Login is immediately reversed; "account deactivated" message shown; user is logged out</t>
+  </si>
+  <si>
+    <t>AUTH-08</t>
+  </si>
+  <si>
+    <t>Logout</t>
+  </si>
+  <si>
+    <t>1. While logged in, click Logout</t>
+  </si>
+  <si>
+    <t>Session invalidated and token regenerated; redirected to /login</t>
+  </si>
+  <si>
+    <t>AUTH-09</t>
+  </si>
+  <si>
+    <t>Forgot password request</t>
+  </si>
+  <si>
+    <t>1. Go to /forgot-password
 2. Submit a registered email</t>
   </si>
   <si>
-    <t xml:space="preserve">Reset link emailed; success status message shown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTH-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reset password via emailed link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the emailed reset link
+    <t>Reset link emailed; success status message shown</t>
+  </si>
+  <si>
+    <t>AUTH-10</t>
+  </si>
+  <si>
+    <t>Reset password via emailed link</t>
+  </si>
+  <si>
+    <t>1. Open the emailed reset link
 2. Enter and confirm a new password
 3. Submit</t>
   </si>
   <si>
-    <t xml:space="preserve">Password updated; can log in with new password; old password no longer works</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USER-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin creates a parent account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login as admin
+    <t>Password updated; can log in with new password; old password no longer works</t>
+  </si>
+  <si>
+    <t>USER-01</t>
+  </si>
+  <si>
+    <t>Admin creates a parent account</t>
+  </si>
+  <si>
+    <t>1. Login as admin
 2. Go to Create User
 3. Select role=Parent, fill fields, submit</t>
   </si>
   <si>
-    <t xml:space="preserve">User + parents profile row created together in one transaction; Spatie parent role assigned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USER-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin creates a staff account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Same as USER-01 with role=Staff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User + staff profile row created; Spatie staff role assigned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USER-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin creates another admin account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Same as USER-01 with role=Admin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User row created with admin role; no profile table row required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USER-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-admin blocked from user creation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login as staff or parent
+    <t>User + parents profile row created together in one transaction; Spatie parent role assigned</t>
+  </si>
+  <si>
+    <t>USER-02</t>
+  </si>
+  <si>
+    <t>Admin creates a staff account</t>
+  </si>
+  <si>
+    <t>1. Same as USER-01 with role=Staff</t>
+  </si>
+  <si>
+    <t>User + staff profile row created; Spatie staff role assigned</t>
+  </si>
+  <si>
+    <t>USER-03</t>
+  </si>
+  <si>
+    <t>Admin creates another admin account</t>
+  </si>
+  <si>
+    <t>1. Same as USER-01 with role=Admin</t>
+  </si>
+  <si>
+    <t>User row created with admin role; no profile table row required</t>
+  </si>
+  <si>
+    <t>USER-04</t>
+  </si>
+  <si>
+    <t>Non-admin blocked from user creation</t>
+  </si>
+  <si>
+    <t>1. Login as staff or parent
 2. Attempt to visit /users/create directly</t>
   </si>
   <si>
-    <t xml:space="preserve">Access denied (403) or redirected away</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PERM-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin sees full sidebar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login as admin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every module (Programs, Children, Billing, Staff, Reports, Settings, etc.) appears in the sidebar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PERM-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff sees operational-only sidebar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login as staff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff mgmt, Reports, Settings hidden; operational items (Attendance, Daily Logs, Activities) visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PERM-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parent sees read-only sidebar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login as parent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only view-permitted items appear (own children, invoices, announcements); no create/manage items shown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PERM-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menu item on an unbuilt route doesn't crash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. As admin, click a sidebar item still using a raw url (not yet a named route)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Page loads (404 if controller isn't built); shared layout never throws a RouteNotFoundException</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PERM-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revoking a permission updates the menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Remove a permission from the staff role
+    <t>Access denied (403) or redirected away</t>
+  </si>
+  <si>
+    <t>PERM-01</t>
+  </si>
+  <si>
+    <t>Admin sees full sidebar</t>
+  </si>
+  <si>
+    <t>1. Login as admin</t>
+  </si>
+  <si>
+    <t>Every module (Programs, Children, Billing, Staff, Reports, Settings, etc.) appears in the sidebar</t>
+  </si>
+  <si>
+    <t>PERM-02</t>
+  </si>
+  <si>
+    <t>Staff sees operational-only sidebar</t>
+  </si>
+  <si>
+    <t>1. Login as staff</t>
+  </si>
+  <si>
+    <t>Staff mgmt, Reports, Settings hidden; operational items (Attendance, Daily Logs, Activities) visible</t>
+  </si>
+  <si>
+    <t>PERM-03</t>
+  </si>
+  <si>
+    <t>Parent sees read-only sidebar</t>
+  </si>
+  <si>
+    <t>1. Login as parent</t>
+  </si>
+  <si>
+    <t>Only view-permitted items appear (own children, invoices, announcements); no create/manage items shown</t>
+  </si>
+  <si>
+    <t>PERM-04</t>
+  </si>
+  <si>
+    <t>Menu item on an unbuilt route doesn't crash</t>
+  </si>
+  <si>
+    <t>1. As admin, click a sidebar item still using a raw url (not yet a named route)</t>
+  </si>
+  <si>
+    <t>Page loads (404 if controller isn't built); shared layout never throws a RouteNotFoundException</t>
+  </si>
+  <si>
+    <t>PERM-05</t>
+  </si>
+  <si>
+    <t>Revoking a permission updates the menu</t>
+  </si>
+  <si>
+    <t>1. Remove a permission from the staff role
 2. Log out and back in as a staff user</t>
   </si>
   <si>
-    <t xml:space="preserve">The corresponding sidebar item is no longer visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHILD-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create a child links a guardian automatically</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Admin/staff creates a new child under a parent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A guardian_child row is auto-created linking the billing parent, accepted_at set, access_level=full</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHILD-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parent sees only their own children</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login as a parent with 1+ children
+    <t>The corresponding sidebar item is no longer visible</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>CHILD-01</t>
+  </si>
+  <si>
+    <t>Create a child links a guardian automatically</t>
+  </si>
+  <si>
+    <t>1. Admin/staff creates a new child under a parent</t>
+  </si>
+  <si>
+    <t>A guardian_child row is auto-created linking the billing parent, accepted_at set, access_level=full</t>
+  </si>
+  <si>
+    <t>CHILD-02</t>
+  </si>
+  <si>
+    <t>Parent sees only their own children</t>
+  </si>
+  <si>
+    <t>1. Login as a parent with 1+ children
 2. Go to Children index</t>
   </si>
   <si>
-    <t xml:space="preserve">Only that parent's linked children appear; no other family's children</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHILD-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parent blocked from another family's child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. As a parent, note another family's child ID
+    <t>Only that parent's linked children appear; no other family's children</t>
+  </si>
+  <si>
+    <t>CHILD-03</t>
+  </si>
+  <si>
+    <t>Parent blocked from another family's child</t>
+  </si>
+  <si>
+    <t>1. As a parent, note another family's child ID
 2. Visit /children/{id} directly</t>
   </si>
   <si>
-    <t xml:space="preserve">403 Forbidden — ChildPolicy blocks it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHILD-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff sees all active children</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login as staff
+    <t>403 Forbidden — ChildPolicy blocks it</t>
+  </si>
+  <si>
+    <t>CHILD-04</t>
+  </si>
+  <si>
+    <t>Staff sees all active children</t>
+  </si>
+  <si>
+    <t>1. Login as staff
 2. Go to Children index</t>
   </si>
   <si>
-    <t xml:space="preserve">All is_active=true children appear regardless of family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHILD-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edit a child record</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Admin/staff opens a child
+    <t>All is_active=true children appear regardless of family</t>
+  </si>
+  <si>
+    <t>CHILD-05</t>
+  </si>
+  <si>
+    <t>Edit a child record</t>
+  </si>
+  <si>
+    <t>1. Admin/staff opens a child
 2. Updates a field (e.g. allergies)
 3. Saves</t>
   </si>
   <si>
-    <t xml:space="preserve">Update persists and displays correctly on reload</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHILD-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View-only guardian blocked from editing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. A guardian with access_level=view_only attempts to edit the child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edit action is blocked by policy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHILD-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deactivate a child (soft delete)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Admin deactivates a child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_active becomes false; attendance/billing history remains intact, not deleted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHILD-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emergency contact fields save correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill ec_name, ec_relationship, ec_phone, ec_authorized_pickup
+    <t>Update persists and displays correctly on reload</t>
+  </si>
+  <si>
+    <t>CHILD-06</t>
+  </si>
+  <si>
+    <t>View-only guardian blocked from editing</t>
+  </si>
+  <si>
+    <t>1. A guardian with access_level=view_only attempts to edit the child</t>
+  </si>
+  <si>
+    <t>Edit action is blocked by policy</t>
+  </si>
+  <si>
+    <t>CHILD-07</t>
+  </si>
+  <si>
+    <t>Deactivate a child (soft delete)</t>
+  </si>
+  <si>
+    <t>1. Admin deactivates a child</t>
+  </si>
+  <si>
+    <t>is_active becomes false; attendance/billing history remains intact, not deleted</t>
+  </si>
+  <si>
+    <t>CHILD-08</t>
+  </si>
+  <si>
+    <t>Emergency contact fields save correctly</t>
+  </si>
+  <si>
+    <t>1. Fill ec_name, ec_relationship, ec_phone, ec_authorized_pickup
 2. Save and reopen</t>
   </si>
   <si>
-    <t xml:space="preserve">All four fields display exactly as entered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GUARD-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pending guardian invite has no access yet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add a second guardian to a child with accepted_at left null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">That guardian cannot see the child in their account yet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GUARD-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accepted guardian gains access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Set accepted_at on that guardian_child row (simulating acceptance)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The guardian can now view the child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GUARD-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">can_pickup flag reflected correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Set can_pickup=false for a guardian
+    <t>All four fields display exactly as entered</t>
+  </si>
+  <si>
+    <t>GUARD-01</t>
+  </si>
+  <si>
+    <t>Pending guardian invite has no access yet</t>
+  </si>
+  <si>
+    <t>1. Add a second guardian to a child with accepted_at left null</t>
+  </si>
+  <si>
+    <t>That guardian cannot see the child in their account yet</t>
+  </si>
+  <si>
+    <t>GUARD-02</t>
+  </si>
+  <si>
+    <t>Accepted guardian gains access</t>
+  </si>
+  <si>
+    <t>1. Set accepted_at on that guardian_child row (simulating acceptance)</t>
+  </si>
+  <si>
+    <t>The guardian can now view the child</t>
+  </si>
+  <si>
+    <t>GUARD-03</t>
+  </si>
+  <si>
+    <t>can_pickup flag reflected correctly</t>
+  </si>
+  <si>
+    <t>1. Set can_pickup=false for a guardian
 2. Check wherever pickup authorization is displayed</t>
   </si>
   <si>
-    <t xml:space="preserve">Correctly shown as not authorized for pickup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GUARD-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary guardian flag is accurate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Check is_primary on the auto-created guardian_child row from CHILD-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The billing parent is marked is_primary=true</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create a new program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Admin creates a program with name, age range, capacity, billing model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Program saved and appears in the catalog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROG-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State-funded program shows $0 fee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Create/view a program with billing_model=state_funded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monthly_fee displays as $0 / not applicable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROG-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deactivated program hidden from enrollment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Set a program's is_active=false
+    <t>Correctly shown as not authorized for pickup</t>
+  </si>
+  <si>
+    <t>GUARD-04</t>
+  </si>
+  <si>
+    <t>Primary guardian flag is accurate</t>
+  </si>
+  <si>
+    <t>1. Check is_primary on the auto-created guardian_child row from CHILD-01</t>
+  </si>
+  <si>
+    <t>The billing parent is marked is_primary=true</t>
+  </si>
+  <si>
+    <t>PROG-01</t>
+  </si>
+  <si>
+    <t>Create a new program</t>
+  </si>
+  <si>
+    <t>1. Admin creates a program with name, age range, capacity, billing model</t>
+  </si>
+  <si>
+    <t>Program saved and appears in the catalog</t>
+  </si>
+  <si>
+    <t>PROG-02</t>
+  </si>
+  <si>
+    <t>State-funded program shows $0 fee</t>
+  </si>
+  <si>
+    <t>1. Create/view a program with billing_model=state_funded</t>
+  </si>
+  <si>
+    <t>monthly_fee displays as $0 / not applicable</t>
+  </si>
+  <si>
+    <t>PROG-03</t>
+  </si>
+  <si>
+    <t>Deactivated program hidden from enrollment</t>
+  </si>
+  <si>
+    <t>1. Set a program's is_active=false
 2. Start a new enrollment</t>
   </si>
   <si>
-    <t xml:space="preserve">That program no longer appears as a selectable option</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROG-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drop-in program uses daily_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Create a program with service_type=drop_in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">daily_rate field is used/required; monthly_fee stays empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROG-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-admin blocked from managing programs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login as staff or parent
+    <t>That program no longer appears as a selectable option</t>
+  </si>
+  <si>
+    <t>PROG-04</t>
+  </si>
+  <si>
+    <t>Drop-in program uses daily_rate</t>
+  </si>
+  <si>
+    <t>1. Create a program with service_type=drop_in</t>
+  </si>
+  <si>
+    <t>daily_rate field is used/required; monthly_fee stays empty</t>
+  </si>
+  <si>
+    <t>PROG-05</t>
+  </si>
+  <si>
+    <t>Non-admin blocked from managing programs</t>
+  </si>
+  <si>
+    <t>1. Login as staff or parent
 2. Attempt to create/edit a program</t>
   </si>
   <si>
-    <t xml:space="preserve">Access denied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENR-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enroll within age range succeeds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enroll a child whose age fits the program's min/max_age_months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enrollment created with status=pending or active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENR-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enroll outside age range blocked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Attempt to enroll a child outside the program's age range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation/business rule blocks it with a clear message</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENR-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enrollment at full capacity goes to waitlist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enroll into a program already at its capacity limit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Child is routed to the waitlist instead of being enrolled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENR-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status progression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Move an enrollment from pending → approved → active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each transition saves correctly; approved_at/approved_by populate on approval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENR-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Withdraw an active enrollment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Withdraw a currently active enrollment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">status becomes withdrawn; end_date is recorded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENR-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enrolled_by is recorded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Submit a new enrollment as a specific admin/staff user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enrolled_by correctly stores that user's ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAIT-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waitlist position assigned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add a child to a full program's waitlist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A position number is assigned (e.g. next available)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAIT-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Offer a waitlist slot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. A spot opens; change status from waiting to offered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status updates correctly; child is notified per your process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAIT-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expired offer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Let an offered waitlist entry pass its response window</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status updates to expired</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATT-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check in a child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Staff checks in a child for today</t>
-  </si>
-  <si>
-    <t xml:space="preserve">check_in_time recorded; status=present</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATT-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check out a child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Staff checks out the same child later</t>
-  </si>
-  <si>
-    <t xml:space="preserve">check_out_time recorded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATT-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark absent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Mark a child absent for a day they didn't attend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">status=absent saved for that date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATT-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily attendance counts are accurate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Compare the attendance report for a given day against manual check-ins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Present/absent/late counts match reality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log a nap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add a daily log with log_type=nap, start/end time, quality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entry saves and displays correctly on the child's timeline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOG-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log a meal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add a daily log with log_type=meal, meal_type, items_served, amount_eaten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meal-specific fields save; unrelated fields (quality) stay blank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOG-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log activity participation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Log an entry with log_type=activity linked to an activity_occurrence_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entry correctly references the occurrence; shows in that occurrence's participant list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOG-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log an incident</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add a daily log with log_type=incident and detailed notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes saved in full; visible to authorized staff/admin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOG-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily timeline sorts correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. View a child's full day of logs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entries display in chronological order by start_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOG-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parent has read-only access to logs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login as parent
+    <t>Access denied</t>
+  </si>
+  <si>
+    <t>ENR-01</t>
+  </si>
+  <si>
+    <t>Enroll within age range succeeds</t>
+  </si>
+  <si>
+    <t>1. Enroll a child whose age fits the program's min/max_age_months</t>
+  </si>
+  <si>
+    <t>Enrollment created with status=pending or active</t>
+  </si>
+  <si>
+    <t>ENR-02</t>
+  </si>
+  <si>
+    <t>Enroll outside age range blocked</t>
+  </si>
+  <si>
+    <t>1. Attempt to enroll a child outside the program's age range</t>
+  </si>
+  <si>
+    <t>Validation/business rule blocks it with a clear message</t>
+  </si>
+  <si>
+    <t>ENR-03</t>
+  </si>
+  <si>
+    <t>Enrollment at full capacity goes to waitlist</t>
+  </si>
+  <si>
+    <t>1. Enroll into a program already at its capacity limit</t>
+  </si>
+  <si>
+    <t>Child is routed to the waitlist instead of being enrolled</t>
+  </si>
+  <si>
+    <t>ENR-04</t>
+  </si>
+  <si>
+    <t>Status progression</t>
+  </si>
+  <si>
+    <t>1. Move an enrollment from pending → approved → active</t>
+  </si>
+  <si>
+    <t>Each transition saves correctly; approved_at/approved_by populate on approval</t>
+  </si>
+  <si>
+    <t>ENR-05</t>
+  </si>
+  <si>
+    <t>Withdraw an active enrollment</t>
+  </si>
+  <si>
+    <t>1. Withdraw a currently active enrollment</t>
+  </si>
+  <si>
+    <t>status becomes withdrawn; end_date is recorded</t>
+  </si>
+  <si>
+    <t>ENR-06</t>
+  </si>
+  <si>
+    <t>enrolled_by is recorded</t>
+  </si>
+  <si>
+    <t>1. Submit a new enrollment as a specific admin/staff user</t>
+  </si>
+  <si>
+    <t>enrolled_by correctly stores that user's ID</t>
+  </si>
+  <si>
+    <t>WAIT-01</t>
+  </si>
+  <si>
+    <t>Waitlist position assigned</t>
+  </si>
+  <si>
+    <t>1. Add a child to a full program's waitlist</t>
+  </si>
+  <si>
+    <t>A position number is assigned (e.g. next available)</t>
+  </si>
+  <si>
+    <t>WAIT-02</t>
+  </si>
+  <si>
+    <t>Offer a waitlist slot</t>
+  </si>
+  <si>
+    <t>1. A spot opens; change status from waiting to offered</t>
+  </si>
+  <si>
+    <t>Status updates correctly; child is notified per your process</t>
+  </si>
+  <si>
+    <t>WAIT-03</t>
+  </si>
+  <si>
+    <t>Expired offer</t>
+  </si>
+  <si>
+    <t>1. Let an offered waitlist entry pass its response window</t>
+  </si>
+  <si>
+    <t>Status updates to expired</t>
+  </si>
+  <si>
+    <t>ATT-01</t>
+  </si>
+  <si>
+    <t>Check in a child</t>
+  </si>
+  <si>
+    <t>1. Staff checks in a child for today</t>
+  </si>
+  <si>
+    <t>check_in_time recorded; status=present</t>
+  </si>
+  <si>
+    <t>ATT-02</t>
+  </si>
+  <si>
+    <t>Check out a child</t>
+  </si>
+  <si>
+    <t>1. Staff checks out the same child later</t>
+  </si>
+  <si>
+    <t>check_out_time recorded</t>
+  </si>
+  <si>
+    <t>ATT-03</t>
+  </si>
+  <si>
+    <t>Mark absent</t>
+  </si>
+  <si>
+    <t>1. Mark a child absent for a day they didn't attend</t>
+  </si>
+  <si>
+    <t>status=absent saved for that date</t>
+  </si>
+  <si>
+    <t>ATT-04</t>
+  </si>
+  <si>
+    <t>Daily attendance counts are accurate</t>
+  </si>
+  <si>
+    <t>1. Compare the attendance report for a given day against manual check-ins</t>
+  </si>
+  <si>
+    <t>Present/absent/late counts match reality</t>
+  </si>
+  <si>
+    <t>LOG-01</t>
+  </si>
+  <si>
+    <t>Log a nap</t>
+  </si>
+  <si>
+    <t>1. Add a daily log with log_type=nap, start/end time, quality</t>
+  </si>
+  <si>
+    <t>Entry saves and displays correctly on the child's timeline</t>
+  </si>
+  <si>
+    <t>LOG-02</t>
+  </si>
+  <si>
+    <t>Log a meal</t>
+  </si>
+  <si>
+    <t>1. Add a daily log with log_type=meal, meal_type, items_served, amount_eaten</t>
+  </si>
+  <si>
+    <t>Meal-specific fields save; unrelated fields (quality) stay blank</t>
+  </si>
+  <si>
+    <t>LOG-03</t>
+  </si>
+  <si>
+    <t>Log activity participation</t>
+  </si>
+  <si>
+    <t>1. Log an entry with log_type=activity linked to an activity_occurrence_id</t>
+  </si>
+  <si>
+    <t>Entry correctly references the occurrence; shows in that occurrence's participant list</t>
+  </si>
+  <si>
+    <t>LOG-04</t>
+  </si>
+  <si>
+    <t>Log an incident</t>
+  </si>
+  <si>
+    <t>1. Add a daily log with log_type=incident and detailed notes</t>
+  </si>
+  <si>
+    <t>Notes saved in full; visible to authorized staff/admin</t>
+  </si>
+  <si>
+    <t>LOG-05</t>
+  </si>
+  <si>
+    <t>Daily timeline sorts correctly</t>
+  </si>
+  <si>
+    <t>1. View a child's full day of logs</t>
+  </si>
+  <si>
+    <t>Entries display in chronological order by start_time</t>
+  </si>
+  <si>
+    <t>LOG-06</t>
+  </si>
+  <si>
+    <t>Parent has read-only access to logs</t>
+  </si>
+  <si>
+    <t>1. Login as parent
 2. View own child's daily logs</t>
   </si>
   <si>
-    <t xml:space="preserve">Logs are visible but no edit controls are shown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOC-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upload a document</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Admin/staff uploads an immunization record for a child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File stored; document row created with correct doc_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOC-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expiry date displays</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Upload a document with an expiry_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expiry date shows correctly on the child's document list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOC-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parent cannot upload documents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login as parent
+    <t>Logs are visible but no edit controls are shown</t>
+  </si>
+  <si>
+    <t>DOC-01</t>
+  </si>
+  <si>
+    <t>Upload a document</t>
+  </si>
+  <si>
+    <t>1. Admin/staff uploads an immunization record for a child</t>
+  </si>
+  <si>
+    <t>File stored; document row created with correct doc_type</t>
+  </si>
+  <si>
+    <t>DOC-02</t>
+  </si>
+  <si>
+    <t>Expiry date displays</t>
+  </si>
+  <si>
+    <t>1. Upload a document with an expiry_date</t>
+  </si>
+  <si>
+    <t>Expiry date shows correctly on the child's document list</t>
+  </si>
+  <si>
+    <t>DOC-03</t>
+  </si>
+  <si>
+    <t>Parent cannot upload documents</t>
+  </si>
+  <si>
+    <t>1. Login as parent
 2. Attempt to upload a document</t>
   </si>
   <si>
-    <t xml:space="preserve">Action blocked/hidden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACT-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create an activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Admin adds a new activity to the catalog (name, category, age range)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Activity saved and available for scheduling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACT-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log an activity occurrence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Schedule/log an occurrence for a program on a specific date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occurrence saved with correct activity, program, date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACT-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occurrence status update</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Mark an occurrence as completed / partial / cancelled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status saves correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACT-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monthly calendar view</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the admin's monthly activity view for a given month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All occurrences for that month display grouped by day, matching actual records</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACT-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attach media to an occurrence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Upload a photo/video to an activity occurrence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media saves and displays linked to that occurrence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACT-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Child engagement reflected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Log a child's engagement quality for an activity via the daily log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correct engagement level shows against that child + occurrence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DROP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Book drop-in for enrolled child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Book a drop-in day for a child who already has an active enrollment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Booking created and linked to that child/parent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DROP-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Book drop-in for a walk-in (no account)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Create a drop-in booking with child_id and parent_id left blank, just contact notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Booking saves successfully with both FKs null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DROP-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Move a booking from booked → checked_in → completed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each status transition saves correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DROP-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drop-in appears in manual invoice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Create a manual invoice and select a completed drop-in booking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Line item is added with the correct daily_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BILL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create a daycare-only invoice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Admin selects only active enrollment items for a child
+    <t>Action blocked/hidden</t>
+  </si>
+  <si>
+    <t>ACT-01</t>
+  </si>
+  <si>
+    <t>Create an activity</t>
+  </si>
+  <si>
+    <t>1. Admin adds a new activity to the catalog (name, category, age range)</t>
+  </si>
+  <si>
+    <t>Activity saved and available for scheduling</t>
+  </si>
+  <si>
+    <t>ACT-02</t>
+  </si>
+  <si>
+    <t>Log an activity occurrence</t>
+  </si>
+  <si>
+    <t>1. Schedule/log an occurrence for a program on a specific date</t>
+  </si>
+  <si>
+    <t>Occurrence saved with correct activity, program, date</t>
+  </si>
+  <si>
+    <t>ACT-03</t>
+  </si>
+  <si>
+    <t>Occurrence status update</t>
+  </si>
+  <si>
+    <t>1. Mark an occurrence as completed / partial / cancelled</t>
+  </si>
+  <si>
+    <t>Status saves correctly</t>
+  </si>
+  <si>
+    <t>ACT-04</t>
+  </si>
+  <si>
+    <t>Monthly calendar view</t>
+  </si>
+  <si>
+    <t>1. Open the admin's monthly activity view for a given month</t>
+  </si>
+  <si>
+    <t>All occurrences for that month display grouped by day, matching actual records</t>
+  </si>
+  <si>
+    <t>ACT-05</t>
+  </si>
+  <si>
+    <t>Attach media to an occurrence</t>
+  </si>
+  <si>
+    <t>1. Upload a photo/video to an activity occurrence</t>
+  </si>
+  <si>
+    <t>Media saves and displays linked to that occurrence</t>
+  </si>
+  <si>
+    <t>ACT-06</t>
+  </si>
+  <si>
+    <t>Child engagement reflected</t>
+  </si>
+  <si>
+    <t>1. Log a child's engagement quality for an activity via the daily log</t>
+  </si>
+  <si>
+    <t>Correct engagement level shows against that child + occurrence</t>
+  </si>
+  <si>
+    <t>DROP-01</t>
+  </si>
+  <si>
+    <t>Book drop-in for enrolled child</t>
+  </si>
+  <si>
+    <t>1. Book a drop-in day for a child who already has an active enrollment</t>
+  </si>
+  <si>
+    <t>Booking created and linked to that child/parent</t>
+  </si>
+  <si>
+    <t>DROP-02</t>
+  </si>
+  <si>
+    <t>Book drop-in for a walk-in (no account)</t>
+  </si>
+  <si>
+    <t>1. Create a drop-in booking with child_id and parent_id left blank, just contact notes</t>
+  </si>
+  <si>
+    <t>Booking saves successfully with both FKs null</t>
+  </si>
+  <si>
+    <t>DROP-03</t>
+  </si>
+  <si>
+    <t>1. Move a booking from booked → checked_in → completed</t>
+  </si>
+  <si>
+    <t>Each status transition saves correctly</t>
+  </si>
+  <si>
+    <t>DROP-04</t>
+  </si>
+  <si>
+    <t>Drop-in appears in manual invoice</t>
+  </si>
+  <si>
+    <t>1. Create a manual invoice and select a completed drop-in booking</t>
+  </si>
+  <si>
+    <t>Line item is added with the correct daily_rate</t>
+  </si>
+  <si>
+    <t>BILL-01</t>
+  </si>
+  <si>
+    <t>Create a daycare-only invoice</t>
+  </si>
+  <si>
+    <t>1. Admin selects only active enrollment items for a child
 2. Creates the invoice</t>
   </si>
   <si>
-    <t xml:space="preserve">Invoice type saves as "daycare"; total matches sum of selected items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BILL-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoice type auto-classification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Repeat BILL-01 exactly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type field correctly equals "daycare" (not therapy or mixed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BILL-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Record a full payment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Record a payment equal to the invoice total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoice status updates to paid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BILL-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Record a partial payment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Record a payment less than the invoice total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoice remains outstanding for the correct remaining balance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BILL-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State-funded line item is $0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Include a state-funded enrollment on an invoice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Line item shows unit_price/subtotal = 0.00 correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BILL-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoice item math is correct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add multiple items with different quantities/prices to one invoice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">subtotal and invoice total_amount both calculate correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THER-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create a therapist staff record</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Admin creates a staff user with role=therapist and a specialization (SLT/ABA/OT)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff row saves with correct role, department=therapy, specialization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THER-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Therapy service catalog entry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Admin adds a therapy service (e.g. "ABA Session") with duration and session_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service saves and is selectable for booking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THER-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Existing staff unaffected by new columns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open a staff record created before this module existed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">department defaults to "daycare"; specialization is null; nothing else changed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THER-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-admin blocked from managing services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login as staff/parent
+    <t>Invoice type saves as "daycare"; total matches sum of selected items</t>
+  </si>
+  <si>
+    <t>BILL-02</t>
+  </si>
+  <si>
+    <t>Invoice type auto-classification</t>
+  </si>
+  <si>
+    <t>1. Repeat BILL-01 exactly</t>
+  </si>
+  <si>
+    <t>type field correctly equals "daycare" (not therapy or mixed)</t>
+  </si>
+  <si>
+    <t>BILL-03</t>
+  </si>
+  <si>
+    <t>Record a full payment</t>
+  </si>
+  <si>
+    <t>1. Record a payment equal to the invoice total</t>
+  </si>
+  <si>
+    <t>Invoice status updates to paid</t>
+  </si>
+  <si>
+    <t>BILL-04</t>
+  </si>
+  <si>
+    <t>Record a partial payment</t>
+  </si>
+  <si>
+    <t>1. Record a payment less than the invoice total</t>
+  </si>
+  <si>
+    <t>Invoice remains outstanding for the correct remaining balance</t>
+  </si>
+  <si>
+    <t>BILL-05</t>
+  </si>
+  <si>
+    <t>State-funded line item is $0</t>
+  </si>
+  <si>
+    <t>1. Include a state-funded enrollment on an invoice</t>
+  </si>
+  <si>
+    <t>Line item shows unit_price/subtotal = 0.00 correctly</t>
+  </si>
+  <si>
+    <t>BILL-06</t>
+  </si>
+  <si>
+    <t>Invoice item math is correct</t>
+  </si>
+  <si>
+    <t>1. Add multiple items with different quantities/prices to one invoice</t>
+  </si>
+  <si>
+    <t>subtotal and invoice total_amount both calculate correctly</t>
+  </si>
+  <si>
+    <t>THER-01</t>
+  </si>
+  <si>
+    <t>Create a therapist staff record</t>
+  </si>
+  <si>
+    <t>1. Admin creates a staff user with role=therapist and a specialization (SLT/ABA/OT)</t>
+  </si>
+  <si>
+    <t>Staff row saves with correct role, department=therapy, specialization</t>
+  </si>
+  <si>
+    <t>THER-02</t>
+  </si>
+  <si>
+    <t>Therapy service catalog entry</t>
+  </si>
+  <si>
+    <t>1. Admin adds a therapy service (e.g. "ABA Session") with duration and session_rate</t>
+  </si>
+  <si>
+    <t>Service saves and is selectable for booking</t>
+  </si>
+  <si>
+    <t>THER-03</t>
+  </si>
+  <si>
+    <t>Existing staff unaffected by new columns</t>
+  </si>
+  <si>
+    <t>1. Open a staff record created before this module existed</t>
+  </si>
+  <si>
+    <t>department defaults to "daycare"; specialization is null; nothing else changed</t>
+  </si>
+  <si>
+    <t>THER-04</t>
+  </si>
+  <si>
+    <t>Non-admin blocked from managing services</t>
+  </si>
+  <si>
+    <t>1. Login as staff/parent
 2. Attempt to edit the therapy services catalog</t>
   </si>
   <si>
-    <t xml:space="preserve">TSES-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Book a therapy session</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Book a session for a child with a specific therapist and service, date/time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Session saves with status=scheduled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSES-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark session completed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Update a scheduled session's status to completed, add notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status and notes save correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSES-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark session cancelled/no-show</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Update a session's status to cancelled or no_show</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status saves correctly; session excluded from billing eligibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSES-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multiple same-day sessions allowed (by design)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Book more than 8 sessions for one therapist on the same day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System allows it without blocking — confirms the deliberate "flexible, no hard cap" decision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSES-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">booked_by is recorded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Create a session as a specific logged-in user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">booked_by correctly stores that user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create a single-type package</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Admin creates a package (e.g. "OT — 4 Session Package") with a hand-set price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Package saves; total_sessions derived correctly as 4 from its items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKG-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create a custom combo package</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Admin creates a package with multiple item rows, e.g. 4 OT + 6 ABA + 8 SLT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All item rows save; derived total_sessions = 18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKG-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Package total sessions is accurate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open any package with 2+ item rows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Displayed total equals the sum of session_count across its items — not a separately stored/edited number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKG-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purchase a package for a child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Select a child
+    <t>TSES-01</t>
+  </si>
+  <si>
+    <t>Book a therapy session</t>
+  </si>
+  <si>
+    <t>1. Book a session for a child with a specific therapist and service, date/time</t>
+  </si>
+  <si>
+    <t>Session saves with status=scheduled</t>
+  </si>
+  <si>
+    <t>TSES-02</t>
+  </si>
+  <si>
+    <t>Mark session completed</t>
+  </si>
+  <si>
+    <t>1. Update a scheduled session's status to completed, add notes</t>
+  </si>
+  <si>
+    <t>Status and notes save correctly</t>
+  </si>
+  <si>
+    <t>TSES-03</t>
+  </si>
+  <si>
+    <t>Mark session cancelled/no-show</t>
+  </si>
+  <si>
+    <t>1. Update a session's status to cancelled or no_show</t>
+  </si>
+  <si>
+    <t>Status saves correctly; session excluded from billing eligibility</t>
+  </si>
+  <si>
+    <t>TSES-04</t>
+  </si>
+  <si>
+    <t>Multiple same-day sessions allowed (by design)</t>
+  </si>
+  <si>
+    <t>1. Book more than 8 sessions for one therapist on the same day</t>
+  </si>
+  <si>
+    <t>System allows it without blocking — confirms the deliberate "flexible, no hard cap" decision</t>
+  </si>
+  <si>
+    <t>TSES-05</t>
+  </si>
+  <si>
+    <t>booked_by is recorded</t>
+  </si>
+  <si>
+    <t>1. Create a session as a specific logged-in user</t>
+  </si>
+  <si>
+    <t>booked_by correctly stores that user</t>
+  </si>
+  <si>
+    <t>PKG-01</t>
+  </si>
+  <si>
+    <t>Create a single-type package</t>
+  </si>
+  <si>
+    <t>1. Admin creates a package (e.g. "OT — 4 Session Package") with a hand-set price</t>
+  </si>
+  <si>
+    <t>Package saves; total_sessions derived correctly as 4 from its items</t>
+  </si>
+  <si>
+    <t>PKG-02</t>
+  </si>
+  <si>
+    <t>Create a custom combo package</t>
+  </si>
+  <si>
+    <t>1. Admin creates a package with multiple item rows, e.g. 4 OT + 6 ABA + 8 SLT</t>
+  </si>
+  <si>
+    <t>All item rows save; derived total_sessions = 18</t>
+  </si>
+  <si>
+    <t>PKG-03</t>
+  </si>
+  <si>
+    <t>Package total sessions is accurate</t>
+  </si>
+  <si>
+    <t>1. Open any package with 2+ item rows</t>
+  </si>
+  <si>
+    <t>Displayed total equals the sum of session_count across its items — not a separately stored/edited number</t>
+  </si>
+  <si>
+    <t>PKG-04</t>
+  </si>
+  <si>
+    <t>Purchase a package for a child</t>
+  </si>
+  <si>
+    <t>1. Select a child
 2. Purchase an existing package template</t>
   </si>
   <si>
-    <t xml:space="preserve">A child_therapy_packages row is created with a snapshot of items (child_therapy_package_items)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKG-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purchase price is editable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. During purchase, change the price away from the template's default price
+    <t>A child_therapy_packages row is created with a snapshot of items (child_therapy_package_items)</t>
+  </si>
+  <si>
+    <t>PKG-05</t>
+  </si>
+  <si>
+    <t>Purchase price is editable</t>
+  </si>
+  <si>
+    <t>1. During purchase, change the price away from the template's default price
 2. Save</t>
   </si>
   <si>
-    <t xml:space="preserve">purchase_price stores the edited amount, not the template's original price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKG-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remaining balance calculates correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Complete 2 of 4 included OT sessions for a purchased package
+    <t>purchase_price stores the edited amount, not the template's original price</t>
+  </si>
+  <si>
+    <t>PKG-06</t>
+  </si>
+  <si>
+    <t>Remaining balance calculates correctly</t>
+  </si>
+  <si>
+    <t>1. Complete 2 of 4 included OT sessions for a purchased package
 2. Check remaining balance</t>
   </si>
   <si>
-    <t xml:space="preserve">Remaining shows 2 (included − completed), computed live, not a stored counter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKG-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Book a session against a package</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Book a new therapy session
+    <t>Remaining shows 2 (included − completed), computed live, not a stored counter</t>
+  </si>
+  <si>
+    <t>PKG-07</t>
+  </si>
+  <si>
+    <t>Book a session against a package</t>
+  </si>
+  <si>
+    <t>1. Book a new therapy session
 2. Choose "from package" and select the child's active package</t>
   </si>
   <si>
-    <t xml:space="preserve">Session saves with child_therapy_package_id set to that package</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKG-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Package-sourced session isn't billed again</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Complete a session booked from a package
+    <t>Session saves with child_therapy_package_id set to that package</t>
+  </si>
+  <si>
+    <t>PKG-08</t>
+  </si>
+  <si>
+    <t>Package-sourced session isn't billed again</t>
+  </si>
+  <si>
+    <t>1. Complete a session booked from a package
 2. Open the manual invoice / unbilled sessions screen</t>
   </si>
   <si>
-    <t xml:space="preserve">That session does NOT appear as a standalone billable item — it was already prepaid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKG-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only completed sessions reduce balance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Book a package session
+    <t>That session does NOT appear as a standalone billable item — it was already prepaid</t>
+  </si>
+  <si>
+    <t>PKG-09</t>
+  </si>
+  <si>
+    <t>Only completed sessions reduce balance</t>
+  </si>
+  <si>
+    <t>1. Book a package session
 2. Mark it cancelled or no_show instead of completed
 3. Recheck remaining balance</t>
   </si>
   <si>
-    <t xml:space="preserve">Balance is unchanged — only completed sessions consume from the package</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKG-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oldest package consumed first (FIFO)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Give a child two active packages with the same therapy type
+    <t>Balance is unchanged — only completed sessions consume from the package</t>
+  </si>
+  <si>
+    <t>PKG-10</t>
+  </si>
+  <si>
+    <t>Oldest package consumed first (FIFO)</t>
+  </si>
+  <si>
+    <t>1. Give a child two active packages with the same therapy type
 2. Book a new session from a package</t>
   </si>
   <si>
-    <t xml:space="preserve">The older (earlier purchased_at) package's balance is drawn down first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKG-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leftover balance carries forward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Purchase a second package for a child who still has unused sessions on an older one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both packages remain active independently — no merge/migration; old balance is still usable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKG-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Existing balance shown before new purchase price is set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Start a new package purchase for a child who already has remaining sessions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An info panel shows existing unused sessions before the admin finalizes the price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKG-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cancel a package</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Admin cancels an active child package</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status becomes cancelled; it no longer offers balance for new session bookings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKG-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-admin blocked from package management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login as staff — attempt to create/edit a package or purchase one
+    <t>The older (earlier purchased_at) package's balance is drawn down first</t>
+  </si>
+  <si>
+    <t>PKG-11</t>
+  </si>
+  <si>
+    <t>Leftover balance carries forward</t>
+  </si>
+  <si>
+    <t>1. Purchase a second package for a child who still has unused sessions on an older one</t>
+  </si>
+  <si>
+    <t>Both packages remain active independently — no merge/migration; old balance is still usable</t>
+  </si>
+  <si>
+    <t>PKG-12</t>
+  </si>
+  <si>
+    <t>Existing balance shown before new purchase price is set</t>
+  </si>
+  <si>
+    <t>1. Start a new package purchase for a child who already has remaining sessions</t>
+  </si>
+  <si>
+    <t>An info panel shows existing unused sessions before the admin finalizes the price</t>
+  </si>
+  <si>
+    <t>PKG-13</t>
+  </si>
+  <si>
+    <t>Cancel a package</t>
+  </si>
+  <si>
+    <t>1. Admin cancels an active child package</t>
+  </si>
+  <si>
+    <t>Status becomes cancelled; it no longer offers balance for new session bookings</t>
+  </si>
+  <si>
+    <t>PKG-14</t>
+  </si>
+  <si>
+    <t>Non-admin blocked from package management</t>
+  </si>
+  <si>
+    <t>1. Login as staff — attempt to create/edit a package or purchase one
 2. Login as parent — view own child's package</t>
   </si>
   <si>
-    <t xml:space="preserve">Staff: view-only per therapy-packages permissions; Parent: read-only, own child only; neither can purchase/cancel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBILL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unbilled sessions appear for selection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Complete a therapy session
+    <t>Staff: view-only per therapy-packages permissions; Parent: read-only, own child only; neither can purchase/cancel</t>
+  </si>
+  <si>
+    <t>TBILL-01</t>
+  </si>
+  <si>
+    <t>Unbilled sessions appear for selection</t>
+  </si>
+  <si>
+    <t>1. Complete a therapy session
 2. Open the manual invoice creation screen for that child</t>
   </si>
   <si>
-    <t xml:space="preserve">The completed session appears in the "unbilled" checklist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBILL-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billed session disappears from the unbilled list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Invoice the session from TBILL-01
+    <t>The completed session appears in the "unbilled" checklist</t>
+  </si>
+  <si>
+    <t>TBILL-02</t>
+  </si>
+  <si>
+    <t>Billed session disappears from the unbilled list</t>
+  </si>
+  <si>
+    <t>1. Invoice the session from TBILL-01
 2. Reopen the invoice creation screen for the same child</t>
   </si>
   <si>
-    <t xml:space="preserve">That session no longer appears (whereDoesntHave invoiceItem check works)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBILL-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Therapy-only invoice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Create an invoice selecting only therapy session items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoice type saves as "therapy"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBILL-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mixed invoice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Create an invoice selecting both enrollment and therapy session items together</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoice type saves as "mixed"; both line item types appear on one invoice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBILL-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Package purchase generates one invoice item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Purchase a package for a child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exactly one invoice_item is created immediately, with child_therapy_package_id set (prepaid)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBILL-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Package sessions excluded from per-session billing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Complete several sessions drawn from an active package
+    <t>That session no longer appears (whereDoesntHave invoiceItem check works)</t>
+  </si>
+  <si>
+    <t>TBILL-03</t>
+  </si>
+  <si>
+    <t>Therapy-only invoice</t>
+  </si>
+  <si>
+    <t>1. Create an invoice selecting only therapy session items</t>
+  </si>
+  <si>
+    <t>Invoice type saves as "therapy"</t>
+  </si>
+  <si>
+    <t>TBILL-04</t>
+  </si>
+  <si>
+    <t>Mixed invoice</t>
+  </si>
+  <si>
+    <t>1. Create an invoice selecting both enrollment and therapy session items together</t>
+  </si>
+  <si>
+    <t>Invoice type saves as "mixed"; both line item types appear on one invoice</t>
+  </si>
+  <si>
+    <t>TBILL-05</t>
+  </si>
+  <si>
+    <t>Package purchase generates one invoice item</t>
+  </si>
+  <si>
+    <t>1. Purchase a package for a child</t>
+  </si>
+  <si>
+    <t>Exactly one invoice_item is created immediately, with child_therapy_package_id set (prepaid)</t>
+  </si>
+  <si>
+    <t>TBILL-06</t>
+  </si>
+  <si>
+    <t>Package sessions excluded from per-session billing</t>
+  </si>
+  <si>
+    <t>1. Complete several sessions drawn from an active package
 2. Run the standalone therapy billing screen</t>
   </si>
   <si>
-    <t xml:space="preserve">None of those package-sourced sessions appear in the unbilled list — only true standalone sessions do</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue report totals are accurate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Run the Billing/Revenue report for a known date range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total invoiced/collected/outstanding match a manual sum of those invoices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REP-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue report type filter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Filter the revenue report by type=therapy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only therapy-relevant figures reflect per the intended filter logic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REP-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outstanding invoices list is correct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Run the Outstanding Invoices report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only invoices with status sent/overdue appear, sorted most-overdue first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REP-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days overdue calculation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Check a specific overdue invoice's days_overdue value against today's date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value matches an actual day-count calculation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REP-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoice auto-flip to overdue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Let a sent invoice's due_date pass
+    <t>None of those package-sourced sessions appear in the unbilled list — only true standalone sessions do</t>
+  </si>
+  <si>
+    <t>REP-01</t>
+  </si>
+  <si>
+    <t>Revenue report totals are accurate</t>
+  </si>
+  <si>
+    <t>1. Run the Billing/Revenue report for a known date range</t>
+  </si>
+  <si>
+    <t>Total invoiced/collected/outstanding match a manual sum of those invoices</t>
+  </si>
+  <si>
+    <t>REP-02</t>
+  </si>
+  <si>
+    <t>Revenue report type filter</t>
+  </si>
+  <si>
+    <t>1. Filter the revenue report by type=therapy</t>
+  </si>
+  <si>
+    <t>Only therapy-relevant figures reflect per the intended filter logic</t>
+  </si>
+  <si>
+    <t>REP-03</t>
+  </si>
+  <si>
+    <t>Outstanding invoices list is correct</t>
+  </si>
+  <si>
+    <t>1. Run the Outstanding Invoices report</t>
+  </si>
+  <si>
+    <t>Only invoices with status sent/overdue appear, sorted most-overdue first</t>
+  </si>
+  <si>
+    <t>REP-04</t>
+  </si>
+  <si>
+    <t>Days overdue calculation</t>
+  </si>
+  <si>
+    <t>1. Check a specific overdue invoice's days_overdue value against today's date</t>
+  </si>
+  <si>
+    <t>Value matches an actual day-count calculation</t>
+  </si>
+  <si>
+    <t>REP-05</t>
+  </si>
+  <si>
+    <t>Invoice auto-flip to overdue</t>
+  </si>
+  <si>
+    <t>1. Let a sent invoice's due_date pass
 2. Run the scheduled overdue-check job</t>
   </si>
   <si>
-    <t xml:space="preserve">Status updates from sent to overdue automatically</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REP-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Report totals row</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Check the summary/total row on each report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Totals correctly sum the visible rows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANN-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Audience targeting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Staff posts an announcement with audience=parents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only parent accounts see it; staff/admin-only announcements stay hidden from parents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANN-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expired announcement hides</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Set expires_at to a past date on an announcement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It no longer displays to any audience</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANN-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Permission-gated visibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login as a role without announcements.view-any</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Announcements page/menu item is inaccessible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAFE-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate a safety tag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. From a child's profile, generate a new safety tag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A unique token and QR image are created and saved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAFE-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scan loads the public card</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the QR's URL in a browser with no login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The safety card page loads successfully, no auth required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAFE-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Card shows minimal info only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Inspect the rendered public card</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only first name + phone numbers shown — no last name, no address, no medical notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAFE-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Call Guardian button works</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Tap/click the Call Guardian button on a mobile device</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correct parent phone number is dialed via tel: link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAFE-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Found report with location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Submit "I found this child" and allow location access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Report saves with latitude/longitude populated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAFE-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Found report without location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Submit the same form but deny location permission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Report still saves successfully with lat/lng left null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAFE-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guardian receives the alert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Submit a found report
+    <t>Status updates from sent to overdue automatically</t>
+  </si>
+  <si>
+    <t>REP-06</t>
+  </si>
+  <si>
+    <t>Report totals row</t>
+  </si>
+  <si>
+    <t>1. Check the summary/total row on each report</t>
+  </si>
+  <si>
+    <t>Totals correctly sum the visible rows</t>
+  </si>
+  <si>
+    <t>ANN-01</t>
+  </si>
+  <si>
+    <t>Audience targeting</t>
+  </si>
+  <si>
+    <t>1. Staff posts an announcement with audience=parents</t>
+  </si>
+  <si>
+    <t>Only parent accounts see it; staff/admin-only announcements stay hidden from parents</t>
+  </si>
+  <si>
+    <t>ANN-02</t>
+  </si>
+  <si>
+    <t>Expired announcement hides</t>
+  </si>
+  <si>
+    <t>1. Set expires_at to a past date on an announcement</t>
+  </si>
+  <si>
+    <t>It no longer displays to any audience</t>
+  </si>
+  <si>
+    <t>ANN-03</t>
+  </si>
+  <si>
+    <t>Permission-gated visibility</t>
+  </si>
+  <si>
+    <t>1. Login as a role without announcements.view-any</t>
+  </si>
+  <si>
+    <t>Announcements page/menu item is inaccessible</t>
+  </si>
+  <si>
+    <t>SAFE-01</t>
+  </si>
+  <si>
+    <t>Generate a safety tag</t>
+  </si>
+  <si>
+    <t>1. From a child's profile, generate a new safety tag</t>
+  </si>
+  <si>
+    <t>A unique token and QR image are created and saved</t>
+  </si>
+  <si>
+    <t>SAFE-02</t>
+  </si>
+  <si>
+    <t>Scan loads the public card</t>
+  </si>
+  <si>
+    <t>1. Open the QR's URL in a browser with no login</t>
+  </si>
+  <si>
+    <t>The safety card page loads successfully, no auth required</t>
+  </si>
+  <si>
+    <t>SAFE-03</t>
+  </si>
+  <si>
+    <t>Card shows minimal info only</t>
+  </si>
+  <si>
+    <t>1. Inspect the rendered public card</t>
+  </si>
+  <si>
+    <t>Only first name + phone numbers shown — no last name, no address, no medical notes</t>
+  </si>
+  <si>
+    <t>SAFE-04</t>
+  </si>
+  <si>
+    <t>Call Guardian button works</t>
+  </si>
+  <si>
+    <t>1. Tap/click the Call Guardian button on a mobile device</t>
+  </si>
+  <si>
+    <t>Correct parent phone number is dialed via tel: link</t>
+  </si>
+  <si>
+    <t>SAFE-05</t>
+  </si>
+  <si>
+    <t>Found report with location</t>
+  </si>
+  <si>
+    <t>1. Submit "I found this child" and allow location access</t>
+  </si>
+  <si>
+    <t>Report saves with latitude/longitude populated</t>
+  </si>
+  <si>
+    <t>SAFE-06</t>
+  </si>
+  <si>
+    <t>Found report without location</t>
+  </si>
+  <si>
+    <t>1. Submit the same form but deny location permission</t>
+  </si>
+  <si>
+    <t>Report still saves successfully with lat/lng left null</t>
+  </si>
+  <si>
+    <t>SAFE-07</t>
+  </si>
+  <si>
+    <t>Guardian receives the alert</t>
+  </si>
+  <si>
+    <t>1. Submit a found report
 2. Check the guardian's phone</t>
   </si>
   <si>
-    <t xml:space="preserve">SMS/WhatsApp alert arrives with a map link and finder's contact info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAFE-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deactivated tag returns 404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Deactivate a safety tag
+    <t>SMS/WhatsApp alert arrives with a map link and finder's contact info</t>
+  </si>
+  <si>
+    <t>SAFE-08</t>
+  </si>
+  <si>
+    <t>Deactivated tag returns 404</t>
+  </si>
+  <si>
+    <t>1. Deactivate a safety tag
 2. Revisit its QR URL</t>
   </si>
   <si>
-    <t xml:space="preserve">Page returns 404, does not show stale child data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Session regenerates on login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Inspect the session ID before and after a successful login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Session ID changes after login (fixation protection)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSRF protection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Attempt to submit a POST form without a valid CSRF token</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Request is rejected (419 error)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public routes are rate-limited</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Rapidly hit a public /s/{token} URL more than 30 times in a minute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requests beyond the limit are throttled/rejected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public page is not indexable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. View the safety card page's HTML source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A &lt;meta name="robots" content="noindex, nofollow"&gt; tag is present</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID-guessing is blocked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. As a parent, try sequential child IDs in the URL that aren't theirs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every unauthorized ID returns 403, not the child's data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demo routes removed before production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Check the production route list for any /demo/* AdminLTE routes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None are present</t>
+    <t>Page returns 404, does not show stale child data</t>
+  </si>
+  <si>
+    <t>SEC-01</t>
+  </si>
+  <si>
+    <t>Session regenerates on login</t>
+  </si>
+  <si>
+    <t>1. Inspect the session ID before and after a successful login</t>
+  </si>
+  <si>
+    <t>Session ID changes after login (fixation protection)</t>
+  </si>
+  <si>
+    <t>SEC-02</t>
+  </si>
+  <si>
+    <t>CSRF protection</t>
+  </si>
+  <si>
+    <t>1. Attempt to submit a POST form without a valid CSRF token</t>
+  </si>
+  <si>
+    <t>Request is rejected (419 error)</t>
+  </si>
+  <si>
+    <t>SEC-03</t>
+  </si>
+  <si>
+    <t>Public routes are rate-limited</t>
+  </si>
+  <si>
+    <t>1. Rapidly hit a public /s/{token} URL more than 30 times in a minute</t>
+  </si>
+  <si>
+    <t>Requests beyond the limit are throttled/rejected</t>
+  </si>
+  <si>
+    <t>SEC-04</t>
+  </si>
+  <si>
+    <t>Public page is not indexable</t>
+  </si>
+  <si>
+    <t>1. View the safety card page's HTML source</t>
+  </si>
+  <si>
+    <t>A &lt;meta name="robots" content="noindex, nofollow"&gt; tag is present</t>
+  </si>
+  <si>
+    <t>SEC-05</t>
+  </si>
+  <si>
+    <t>ID-guessing is blocked</t>
+  </si>
+  <si>
+    <t>1. As a parent, try sequential child IDs in the URL that aren't theirs</t>
+  </si>
+  <si>
+    <t>Every unauthorized ID returns 403, not the child's data</t>
+  </si>
+  <si>
+    <t>SEC-06</t>
+  </si>
+  <si>
+    <t>Demo routes removed before production</t>
+  </si>
+  <si>
+    <t>1. Check the production route list for any /demo/* AdminLTE routes</t>
+  </si>
+  <si>
+    <t>None are present</t>
+  </si>
+  <si>
+    <t>User View Needed</t>
+  </si>
+  <si>
+    <t>Child View Needed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0%"/>
-  </numFmts>
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1801,54 +1817,34 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="16"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="10"/>
       <color rgb="FF5B5A55"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -1867,14 +1863,14 @@
     </fill>
   </fills>
   <borders count="3">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFD9D7CE"/>
       </left>
@@ -1889,168 +1885,87 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
-      <top style="double"/>
+      <top style="double">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="5">
     <dxf>
+      <font>
+        <color rgb="FF5F5E5A"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF33322E"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA32D2D"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9F2E6"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1EFE8"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0F6E56"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF5F5E5A"/>
-          <bgColor rgb="FF000000"/>
+        <patternFill>
+          <bgColor rgb="FFF1EFE8"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <color rgb="FF854F0B"/>
         <name val="Arial"/>
         <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEBCF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFA32D2D"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFBDADA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color rgb="FF0F6E56"/>
+        <name val="Arial"/>
+        <charset val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -2060,55 +1975,14 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <color rgb="FFA32D2D"/>
         <name val="Arial"/>
         <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FFA32D2D"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFBDADA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF854F0B"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEBCF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <color rgb="FF5F5E5A"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF1EFE8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FFA32D2D"/>
       </font>
     </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -2167,51 +2041,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF33322E"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -2219,12 +2105,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -2253,7 +2139,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -2274,7 +2160,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -2325,7 +2211,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -2343,176 +2229,173 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="true"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:B26"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="110"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="2:2" ht="20" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B11" s="4"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B13" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B18" s="4"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B21" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B22" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B23" s="4"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B26" s="4" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="true"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:I28"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="2:9" ht="20" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" s="5" t="s">
         <v>23</v>
       </c>
@@ -2538,763 +2421,763 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B6)</f>
+      <c r="C6" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B6)</f>
         <v>10</v>
       </c>
-      <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B6,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+      <c r="D6" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B6,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
         <v>2</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B6,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+      <c r="E6" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B6,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
         <v>8</v>
       </c>
-      <c r="F6" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B6,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B6,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B6,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <f aca="false">IFERROR(E6/C6,0)</f>
+      <c r="F6" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B6,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B6,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B6,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="7">
+        <f t="shared" ref="I6:I28" si="0">IFERROR(E6/C6,0)</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B7)</f>
+      <c r="C7" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B7)</f>
         <v>4</v>
       </c>
-      <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B7,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B7,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+      <c r="D7" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B7,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B7,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
         <v>4</v>
       </c>
-      <c r="F7" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B7,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B7,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B7,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <f aca="false">IFERROR(E7/C7,0)</f>
+      <c r="F7" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B7,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B7,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B7,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B8)</f>
+      <c r="C8" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B8)</f>
         <v>5</v>
       </c>
-      <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B8,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
-        <v>2</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B8,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>3</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B8,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B8,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B8,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <f aca="false">IFERROR(E8/C8,0)</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D8" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B8,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B8,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+        <v>5</v>
+      </c>
+      <c r="F8" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B8,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B8,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B8,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B9)</f>
+      <c r="C9" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B9)</f>
         <v>8</v>
       </c>
-      <c r="D9" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B9,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
-        <v>8</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B9,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B9,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B9,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B9,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <f aca="false">IFERROR(E9/C9,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D9" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B9,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+        <v>5</v>
+      </c>
+      <c r="E9" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B9,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+        <v>3</v>
+      </c>
+      <c r="F9" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B9,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B9,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B9,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="7">
+        <f t="shared" si="0"/>
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B10)</f>
+      <c r="C10" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B10)</f>
         <v>4</v>
       </c>
-      <c r="D10" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B10,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+      <c r="D10" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B10,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
         <v>4</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B10,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B10,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B10,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B10,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <f aca="false">IFERROR(E10/C10,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E10" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B10,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B10,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B10,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B10,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B11)</f>
+      <c r="C11" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B11)</f>
         <v>5</v>
       </c>
-      <c r="D11" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B11,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+      <c r="D11" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B11,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
         <v>5</v>
       </c>
-      <c r="E11" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B11,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B11,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B11,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B11,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <f aca="false">IFERROR(E11/C11,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E11" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B11,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B11,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B11,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B11,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B12)</f>
+      <c r="C12" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B12)</f>
         <v>6</v>
       </c>
-      <c r="D12" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B12,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+      <c r="D12" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B12,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
         <v>6</v>
       </c>
-      <c r="E12" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B12,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B12,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B12,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B12,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <f aca="false">IFERROR(E12/C12,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E12" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B12,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B12,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B12,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B12,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B13" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B13)</f>
+      <c r="C13" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B13)</f>
         <v>3</v>
       </c>
-      <c r="D13" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B13,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+      <c r="D13" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B13,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
         <v>3</v>
       </c>
-      <c r="E13" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B13,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B13,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B13,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B13,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="7" t="n">
-        <f aca="false">IFERROR(E13/C13,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E13" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B13,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B13,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B13,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B13,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B14)</f>
+      <c r="C14" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B14)</f>
         <v>4</v>
       </c>
-      <c r="D14" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B14,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+      <c r="D14" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B14,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
         <v>4</v>
       </c>
-      <c r="E14" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B14,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B14,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B14,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B14,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="7" t="n">
-        <f aca="false">IFERROR(E14/C14,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E14" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B14,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B14,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B14,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B14,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B15" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B15)</f>
+      <c r="C15" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B15)</f>
         <v>6</v>
       </c>
-      <c r="D15" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B15,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+      <c r="D15" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B15,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
         <v>6</v>
       </c>
-      <c r="E15" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B15,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B15,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B15,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B15,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="7" t="n">
-        <f aca="false">IFERROR(E15/C15,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E15" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B15,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B15,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B15,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B15,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B16" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B16)</f>
+      <c r="C16" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B16)</f>
         <v>3</v>
       </c>
-      <c r="D16" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B16,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+      <c r="D16" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B16,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
         <v>3</v>
       </c>
-      <c r="E16" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B16,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B16,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B16,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B16,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <f aca="false">IFERROR(E16/C16,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E16" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B16,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B16,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B16,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B16,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B17" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B17)</f>
+      <c r="C17" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B17)</f>
         <v>6</v>
       </c>
-      <c r="D17" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B17,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+      <c r="D17" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B17,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
         <v>6</v>
       </c>
-      <c r="E17" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B17,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B17,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B17,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B17,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="7" t="n">
-        <f aca="false">IFERROR(E17/C17,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E17" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B17,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B17,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B17,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B17,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B18" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B18)</f>
+      <c r="C18" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B18)</f>
         <v>4</v>
       </c>
-      <c r="D18" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B18,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+      <c r="D18" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B18,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
         <v>4</v>
       </c>
-      <c r="E18" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B18,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B18,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B18,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B18,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="7" t="n">
-        <f aca="false">IFERROR(E18/C18,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E18" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B18,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B18,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B18,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B18,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B19" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B19)</f>
+      <c r="C19" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B19)</f>
         <v>6</v>
       </c>
-      <c r="D19" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B19,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+      <c r="D19" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B19,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
         <v>6</v>
       </c>
-      <c r="E19" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B19,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B19,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B19,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B19,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="7" t="n">
-        <f aca="false">IFERROR(E19/C19,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E19" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B19,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B19,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B19,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B19,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B20" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B20)</f>
+      <c r="C20" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B20)</f>
         <v>4</v>
       </c>
-      <c r="D20" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B20,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+      <c r="D20" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B20,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
         <v>4</v>
       </c>
-      <c r="E20" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B20,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B20,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B20,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B20,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="7" t="n">
-        <f aca="false">IFERROR(E20/C20,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E20" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B20,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B20,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B20,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B20,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B21" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B21)</f>
+      <c r="C21" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B21)</f>
         <v>5</v>
       </c>
-      <c r="D21" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B21,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+      <c r="D21" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B21,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
         <v>5</v>
       </c>
-      <c r="E21" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B21,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B21,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B21,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B21,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="7" t="n">
-        <f aca="false">IFERROR(E21/C21,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E21" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B21,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B21,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B21,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B21,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B22" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B22)</f>
+      <c r="C22" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B22)</f>
         <v>14</v>
       </c>
-      <c r="D22" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B22,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+      <c r="D22" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B22,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
         <v>14</v>
       </c>
-      <c r="E22" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B22,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B22,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B22,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B22,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <f aca="false">IFERROR(E22/C22,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E22" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B22,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B22,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B22,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B22,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B23" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B23)</f>
+      <c r="C23" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B23)</f>
         <v>6</v>
       </c>
-      <c r="D23" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B23,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+      <c r="D23" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B23,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
         <v>6</v>
       </c>
-      <c r="E23" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B23,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B23,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B23,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B23,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I23" s="7" t="n">
-        <f aca="false">IFERROR(E23/C23,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E23" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B23,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B23,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B23,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B23,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B24" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B24)</f>
+      <c r="C24" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B24)</f>
         <v>6</v>
       </c>
-      <c r="D24" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B24,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+      <c r="D24" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B24,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
         <v>6</v>
       </c>
-      <c r="E24" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B24,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B24,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B24,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B24,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="7" t="n">
-        <f aca="false">IFERROR(E24/C24,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E24" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B24,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B24,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B24,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B24,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B25" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B25)</f>
+      <c r="C25" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B25)</f>
         <v>3</v>
       </c>
-      <c r="D25" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B25,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+      <c r="D25" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B25,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
         <v>3</v>
       </c>
-      <c r="E25" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B25,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B25,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B25,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B25,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="7" t="n">
-        <f aca="false">IFERROR(E25/C25,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E25" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B25,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B25,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B25,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B25,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B26" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B26)</f>
+      <c r="C26" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B26)</f>
         <v>8</v>
       </c>
-      <c r="D26" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B26,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+      <c r="D26" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B26,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
         <v>8</v>
       </c>
-      <c r="E26" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B26,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B26,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B26,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B26,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="7" t="n">
-        <f aca="false">IFERROR(E26/C26,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E26" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B26,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B26,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B26,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B26,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B27" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="6" t="n">
-        <f aca="false">COUNTIF('UAT Checklist'!$B$2:$B$127,$B27)</f>
+      <c r="C27" s="6">
+        <f>COUNTIF('UAT Checklist'!$B$2:$B$127,$B27)</f>
         <v>6</v>
       </c>
-      <c r="D27" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B27,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
+      <c r="D27" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B27,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
         <v>6</v>
       </c>
-      <c r="E27" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B27,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B27,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B27,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <f aca="false">COUNTIFS('UAT Checklist'!$B$2:$B$127,$B27,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="7" t="n">
-        <f aca="false">IFERROR(E27/C27,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E27" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B27,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B27,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B27,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="H27" s="6">
+        <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B27,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B28" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="8" t="n">
-        <f aca="false">SUM(C6:C27)</f>
+      <c r="C28" s="8">
+        <f t="shared" ref="C28:H28" si="1">SUM(C6:C27)</f>
         <v>126</v>
       </c>
-      <c r="D28" s="8" t="n">
-        <f aca="false">SUM(D6:D27)</f>
-        <v>111</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <f aca="false">SUM(E6:E27)</f>
-        <v>15</v>
-      </c>
-      <c r="F28" s="8" t="n">
-        <f aca="false">SUM(F6:F27)</f>
-        <v>0</v>
-      </c>
-      <c r="G28" s="8" t="n">
-        <f aca="false">SUM(G6:G27)</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="8" t="n">
-        <f aca="false">SUM(H6:H27)</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="9" t="n">
-        <f aca="false">IFERROR(E28/C28,0)</f>
-        <v>0.119047619047619</v>
+      <c r="D28" s="8">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="E28" s="8">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="F28" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="9">
+        <f t="shared" si="0"/>
+        <v>0.15873015873015872</v>
       </c>
     </row>
   </sheetData>
@@ -3310,38 +3193,33 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="true"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K127"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="36.36328125" customWidth="1"/>
+    <col min="6" max="6" width="33.36328125" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>54</v>
       </c>
@@ -3376,8 +3254,8 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="n">
+    <row r="2" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
@@ -3405,8 +3283,8 @@
       <c r="J2" s="10"/>
       <c r="K2" s="10"/>
     </row>
-    <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="n">
+    <row r="3" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
@@ -3434,8 +3312,8 @@
       <c r="J3" s="10"/>
       <c r="K3" s="10"/>
     </row>
-    <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="n">
+    <row r="4" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
@@ -3463,8 +3341,8 @@
       <c r="J4" s="10"/>
       <c r="K4" s="10"/>
     </row>
-    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="n">
+    <row r="5" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="10">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
@@ -3492,8 +3370,8 @@
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
     </row>
-    <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="n">
+    <row r="6" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="10">
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -3521,8 +3399,8 @@
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
     </row>
-    <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="n">
+    <row r="7" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="10">
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
@@ -3550,8 +3428,8 @@
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
     </row>
-    <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="n">
+    <row r="8" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="10">
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -3579,8 +3457,8 @@
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
     </row>
-    <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="n">
+    <row r="9" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="10">
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
@@ -3608,8 +3486,8 @@
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
     </row>
-    <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="n">
+    <row r="10" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="10">
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
@@ -3637,8 +3515,8 @@
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
     </row>
-    <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="n">
+    <row r="11" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="10">
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
@@ -3666,8 +3544,8 @@
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="n">
+    <row r="12" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="10">
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
@@ -3695,8 +3573,8 @@
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
     </row>
-    <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="n">
+    <row r="13" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="10">
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
@@ -3724,8 +3602,8 @@
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
     </row>
-    <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="n">
+    <row r="14" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="10">
         <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
@@ -3753,8 +3631,8 @@
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
     </row>
-    <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="n">
+    <row r="15" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="10">
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
@@ -3782,8 +3660,8 @@
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
     </row>
-    <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="n">
+    <row r="16" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="10">
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
@@ -3811,8 +3689,8 @@
       <c r="J16" s="10"/>
       <c r="K16" s="10"/>
     </row>
-    <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="n">
+    <row r="17" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="10">
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
@@ -3840,8 +3718,8 @@
       <c r="J17" s="10"/>
       <c r="K17" s="10"/>
     </row>
-    <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="n">
+    <row r="18" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="10">
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
@@ -3869,8 +3747,8 @@
       <c r="J18" s="10"/>
       <c r="K18" s="10"/>
     </row>
-    <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="n">
+    <row r="19" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="10">
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
@@ -3892,14 +3770,14 @@
         <v>77</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I19" s="11"/>
       <c r="J19" s="10"/>
       <c r="K19" s="10"/>
     </row>
-    <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="n">
+    <row r="20" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="10">
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
@@ -3921,14 +3799,14 @@
         <v>142</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I20" s="11"/>
       <c r="J20" s="10"/>
       <c r="K20" s="10"/>
     </row>
-    <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="n">
+    <row r="21" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="10">
         <v>20</v>
       </c>
       <c r="B21" s="11" t="s">
@@ -3950,14 +3828,16 @@
         <v>68</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I21" s="11"/>
+        <v>26</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>569</v>
+      </c>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
     </row>
-    <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="n">
+    <row r="22" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="10">
         <v>21</v>
       </c>
       <c r="B22" s="11" t="s">
@@ -3979,14 +3859,14 @@
         <v>68</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I22" s="11"/>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
     </row>
-    <row r="23" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="n">
+    <row r="23" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="10">
         <v>22</v>
       </c>
       <c r="B23" s="11" t="s">
@@ -4008,14 +3888,16 @@
         <v>68</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I23" s="11"/>
+        <v>26</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>570</v>
+      </c>
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
     </row>
-    <row r="24" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="n">
+    <row r="24" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="10">
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
@@ -4043,8 +3925,8 @@
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
     </row>
-    <row r="25" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10" t="n">
+    <row r="25" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
         <v>24</v>
       </c>
       <c r="B25" s="11" t="s">
@@ -4072,8 +3954,8 @@
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
     </row>
-    <row r="26" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="n">
+    <row r="26" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
         <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
@@ -4101,8 +3983,8 @@
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
     </row>
-    <row r="27" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10" t="n">
+    <row r="27" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="10">
         <v>26</v>
       </c>
       <c r="B27" s="11" t="s">
@@ -4130,8 +4012,8 @@
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
     </row>
-    <row r="28" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10" t="n">
+    <row r="28" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="10">
         <v>27</v>
       </c>
       <c r="B28" s="11" t="s">
@@ -4159,8 +4041,8 @@
       <c r="J28" s="10"/>
       <c r="K28" s="10"/>
     </row>
-    <row r="29" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10" t="n">
+    <row r="29" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="10">
         <v>28</v>
       </c>
       <c r="B29" s="11" t="s">
@@ -4188,8 +4070,8 @@
       <c r="J29" s="10"/>
       <c r="K29" s="10"/>
     </row>
-    <row r="30" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="n">
+    <row r="30" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="10">
         <v>29</v>
       </c>
       <c r="B30" s="11" t="s">
@@ -4217,8 +4099,8 @@
       <c r="J30" s="10"/>
       <c r="K30" s="10"/>
     </row>
-    <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10" t="n">
+    <row r="31" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="10">
         <v>30</v>
       </c>
       <c r="B31" s="11" t="s">
@@ -4246,8 +4128,8 @@
       <c r="J31" s="10"/>
       <c r="K31" s="10"/>
     </row>
-    <row r="32" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10" t="n">
+    <row r="32" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="10">
         <v>31</v>
       </c>
       <c r="B32" s="11" t="s">
@@ -4275,8 +4157,8 @@
       <c r="J32" s="10"/>
       <c r="K32" s="10"/>
     </row>
-    <row r="33" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="10" t="n">
+    <row r="33" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="10">
         <v>32</v>
       </c>
       <c r="B33" s="11" t="s">
@@ -4304,8 +4186,8 @@
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
     </row>
-    <row r="34" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="10" t="n">
+    <row r="34" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="10">
         <v>33</v>
       </c>
       <c r="B34" s="11" t="s">
@@ -4333,8 +4215,8 @@
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
     </row>
-    <row r="35" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10" t="n">
+    <row r="35" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="10">
         <v>34</v>
       </c>
       <c r="B35" s="11" t="s">
@@ -4362,8 +4244,8 @@
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
     </row>
-    <row r="36" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10" t="n">
+    <row r="36" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="10">
         <v>35</v>
       </c>
       <c r="B36" s="11" t="s">
@@ -4391,8 +4273,8 @@
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
     </row>
-    <row r="37" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10" t="n">
+    <row r="37" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="10">
         <v>36</v>
       </c>
       <c r="B37" s="11" t="s">
@@ -4420,8 +4302,8 @@
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
     </row>
-    <row r="38" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="10" t="n">
+    <row r="38" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="10">
         <v>37</v>
       </c>
       <c r="B38" s="11" t="s">
@@ -4449,8 +4331,8 @@
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
     </row>
-    <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10" t="n">
+    <row r="39" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="10">
         <v>38</v>
       </c>
       <c r="B39" s="11" t="s">
@@ -4478,8 +4360,8 @@
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
     </row>
-    <row r="40" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10" t="n">
+    <row r="40" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="10">
         <v>39</v>
       </c>
       <c r="B40" s="11" t="s">
@@ -4507,8 +4389,8 @@
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
     </row>
-    <row r="41" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="10" t="n">
+    <row r="41" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="10">
         <v>40</v>
       </c>
       <c r="B41" s="11" t="s">
@@ -4536,8 +4418,8 @@
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
     </row>
-    <row r="42" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="10" t="n">
+    <row r="42" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="10">
         <v>41</v>
       </c>
       <c r="B42" s="11" t="s">
@@ -4565,8 +4447,8 @@
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
     </row>
-    <row r="43" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="10" t="n">
+    <row r="43" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="10">
         <v>42</v>
       </c>
       <c r="B43" s="11" t="s">
@@ -4594,8 +4476,8 @@
       <c r="J43" s="10"/>
       <c r="K43" s="10"/>
     </row>
-    <row r="44" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="10" t="n">
+    <row r="44" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="10">
         <v>43</v>
       </c>
       <c r="B44" s="11" t="s">
@@ -4623,8 +4505,8 @@
       <c r="J44" s="10"/>
       <c r="K44" s="10"/>
     </row>
-    <row r="45" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="10" t="n">
+    <row r="45" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="10">
         <v>44</v>
       </c>
       <c r="B45" s="11" t="s">
@@ -4652,8 +4534,8 @@
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
     </row>
-    <row r="46" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="10" t="n">
+    <row r="46" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="10">
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
@@ -4681,8 +4563,8 @@
       <c r="J46" s="10"/>
       <c r="K46" s="10"/>
     </row>
-    <row r="47" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="10" t="n">
+    <row r="47" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="10">
         <v>46</v>
       </c>
       <c r="B47" s="11" t="s">
@@ -4710,8 +4592,8 @@
       <c r="J47" s="10"/>
       <c r="K47" s="10"/>
     </row>
-    <row r="48" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="10" t="n">
+    <row r="48" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="10">
         <v>47</v>
       </c>
       <c r="B48" s="11" t="s">
@@ -4739,8 +4621,8 @@
       <c r="J48" s="10"/>
       <c r="K48" s="10"/>
     </row>
-    <row r="49" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="10" t="n">
+    <row r="49" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="10">
         <v>48</v>
       </c>
       <c r="B49" s="11" t="s">
@@ -4768,8 +4650,8 @@
       <c r="J49" s="10"/>
       <c r="K49" s="10"/>
     </row>
-    <row r="50" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="10" t="n">
+    <row r="50" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="10">
         <v>49</v>
       </c>
       <c r="B50" s="11" t="s">
@@ -4797,8 +4679,8 @@
       <c r="J50" s="10"/>
       <c r="K50" s="10"/>
     </row>
-    <row r="51" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="10" t="n">
+    <row r="51" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="10">
         <v>50</v>
       </c>
       <c r="B51" s="11" t="s">
@@ -4826,8 +4708,8 @@
       <c r="J51" s="10"/>
       <c r="K51" s="10"/>
     </row>
-    <row r="52" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="10" t="n">
+    <row r="52" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="10">
         <v>51</v>
       </c>
       <c r="B52" s="11" t="s">
@@ -4855,8 +4737,8 @@
       <c r="J52" s="10"/>
       <c r="K52" s="10"/>
     </row>
-    <row r="53" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="10" t="n">
+    <row r="53" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="10">
         <v>52</v>
       </c>
       <c r="B53" s="11" t="s">
@@ -4884,8 +4766,8 @@
       <c r="J53" s="10"/>
       <c r="K53" s="10"/>
     </row>
-    <row r="54" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="10" t="n">
+    <row r="54" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="10">
         <v>53</v>
       </c>
       <c r="B54" s="11" t="s">
@@ -4913,8 +4795,8 @@
       <c r="J54" s="10"/>
       <c r="K54" s="10"/>
     </row>
-    <row r="55" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="10" t="n">
+    <row r="55" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="10">
         <v>54</v>
       </c>
       <c r="B55" s="11" t="s">
@@ -4942,8 +4824,8 @@
       <c r="J55" s="10"/>
       <c r="K55" s="10"/>
     </row>
-    <row r="56" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="10" t="n">
+    <row r="56" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="10">
         <v>55</v>
       </c>
       <c r="B56" s="11" t="s">
@@ -4971,8 +4853,8 @@
       <c r="J56" s="10"/>
       <c r="K56" s="10"/>
     </row>
-    <row r="57" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="10" t="n">
+    <row r="57" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="10">
         <v>56</v>
       </c>
       <c r="B57" s="11" t="s">
@@ -5000,8 +4882,8 @@
       <c r="J57" s="10"/>
       <c r="K57" s="10"/>
     </row>
-    <row r="58" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="10" t="n">
+    <row r="58" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="10">
         <v>57</v>
       </c>
       <c r="B58" s="11" t="s">
@@ -5029,8 +4911,8 @@
       <c r="J58" s="10"/>
       <c r="K58" s="10"/>
     </row>
-    <row r="59" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="10" t="n">
+    <row r="59" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="10">
         <v>58</v>
       </c>
       <c r="B59" s="11" t="s">
@@ -5058,8 +4940,8 @@
       <c r="J59" s="10"/>
       <c r="K59" s="10"/>
     </row>
-    <row r="60" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="10" t="n">
+    <row r="60" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="10">
         <v>59</v>
       </c>
       <c r="B60" s="11" t="s">
@@ -5087,8 +4969,8 @@
       <c r="J60" s="10"/>
       <c r="K60" s="10"/>
     </row>
-    <row r="61" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="10" t="n">
+    <row r="61" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="10">
         <v>60</v>
       </c>
       <c r="B61" s="11" t="s">
@@ -5116,8 +4998,8 @@
       <c r="J61" s="10"/>
       <c r="K61" s="10"/>
     </row>
-    <row r="62" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="10" t="n">
+    <row r="62" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="10">
         <v>61</v>
       </c>
       <c r="B62" s="11" t="s">
@@ -5145,8 +5027,8 @@
       <c r="J62" s="10"/>
       <c r="K62" s="10"/>
     </row>
-    <row r="63" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="10" t="n">
+    <row r="63" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="10">
         <v>62</v>
       </c>
       <c r="B63" s="11" t="s">
@@ -5174,8 +5056,8 @@
       <c r="J63" s="10"/>
       <c r="K63" s="10"/>
     </row>
-    <row r="64" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="10" t="n">
+    <row r="64" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="10">
         <v>63</v>
       </c>
       <c r="B64" s="11" t="s">
@@ -5203,8 +5085,8 @@
       <c r="J64" s="10"/>
       <c r="K64" s="10"/>
     </row>
-    <row r="65" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="10" t="n">
+    <row r="65" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="10">
         <v>64</v>
       </c>
       <c r="B65" s="11" t="s">
@@ -5232,8 +5114,8 @@
       <c r="J65" s="10"/>
       <c r="K65" s="10"/>
     </row>
-    <row r="66" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="10" t="n">
+    <row r="66" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="10">
         <v>65</v>
       </c>
       <c r="B66" s="11" t="s">
@@ -5261,8 +5143,8 @@
       <c r="J66" s="10"/>
       <c r="K66" s="10"/>
     </row>
-    <row r="67" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="10" t="n">
+    <row r="67" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="10">
         <v>66</v>
       </c>
       <c r="B67" s="11" t="s">
@@ -5290,8 +5172,8 @@
       <c r="J67" s="10"/>
       <c r="K67" s="10"/>
     </row>
-    <row r="68" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="10" t="n">
+    <row r="68" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="10">
         <v>67</v>
       </c>
       <c r="B68" s="11" t="s">
@@ -5319,8 +5201,8 @@
       <c r="J68" s="10"/>
       <c r="K68" s="10"/>
     </row>
-    <row r="69" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="10" t="n">
+    <row r="69" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="10">
         <v>68</v>
       </c>
       <c r="B69" s="11" t="s">
@@ -5348,8 +5230,8 @@
       <c r="J69" s="10"/>
       <c r="K69" s="10"/>
     </row>
-    <row r="70" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="10" t="n">
+    <row r="70" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="10">
         <v>69</v>
       </c>
       <c r="B70" s="11" t="s">
@@ -5377,8 +5259,8 @@
       <c r="J70" s="10"/>
       <c r="K70" s="10"/>
     </row>
-    <row r="71" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="10" t="n">
+    <row r="71" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="10">
         <v>70</v>
       </c>
       <c r="B71" s="11" t="s">
@@ -5406,8 +5288,8 @@
       <c r="J71" s="10"/>
       <c r="K71" s="10"/>
     </row>
-    <row r="72" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="10" t="n">
+    <row r="72" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="10">
         <v>71</v>
       </c>
       <c r="B72" s="11" t="s">
@@ -5435,8 +5317,8 @@
       <c r="J72" s="10"/>
       <c r="K72" s="10"/>
     </row>
-    <row r="73" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="10" t="n">
+    <row r="73" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="10">
         <v>72</v>
       </c>
       <c r="B73" s="11" t="s">
@@ -5464,8 +5346,8 @@
       <c r="J73" s="10"/>
       <c r="K73" s="10"/>
     </row>
-    <row r="74" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="10" t="n">
+    <row r="74" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="10">
         <v>73</v>
       </c>
       <c r="B74" s="11" t="s">
@@ -5493,8 +5375,8 @@
       <c r="J74" s="10"/>
       <c r="K74" s="10"/>
     </row>
-    <row r="75" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="10" t="n">
+    <row r="75" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="10">
         <v>74</v>
       </c>
       <c r="B75" s="11" t="s">
@@ -5522,8 +5404,8 @@
       <c r="J75" s="10"/>
       <c r="K75" s="10"/>
     </row>
-    <row r="76" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="10" t="n">
+    <row r="76" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="10">
         <v>75</v>
       </c>
       <c r="B76" s="11" t="s">
@@ -5551,8 +5433,8 @@
       <c r="J76" s="10"/>
       <c r="K76" s="10"/>
     </row>
-    <row r="77" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="10" t="n">
+    <row r="77" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="10">
         <v>76</v>
       </c>
       <c r="B77" s="11" t="s">
@@ -5580,8 +5462,8 @@
       <c r="J77" s="10"/>
       <c r="K77" s="10"/>
     </row>
-    <row r="78" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="10" t="n">
+    <row r="78" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="10">
         <v>77</v>
       </c>
       <c r="B78" s="11" t="s">
@@ -5609,8 +5491,8 @@
       <c r="J78" s="10"/>
       <c r="K78" s="10"/>
     </row>
-    <row r="79" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="10" t="n">
+    <row r="79" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="10">
         <v>78</v>
       </c>
       <c r="B79" s="11" t="s">
@@ -5638,8 +5520,8 @@
       <c r="J79" s="10"/>
       <c r="K79" s="10"/>
     </row>
-    <row r="80" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="10" t="n">
+    <row r="80" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="10">
         <v>79</v>
       </c>
       <c r="B80" s="11" t="s">
@@ -5667,8 +5549,8 @@
       <c r="J80" s="10"/>
       <c r="K80" s="10"/>
     </row>
-    <row r="81" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="10" t="n">
+    <row r="81" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="10">
         <v>80</v>
       </c>
       <c r="B81" s="11" t="s">
@@ -5696,8 +5578,8 @@
       <c r="J81" s="10"/>
       <c r="K81" s="10"/>
     </row>
-    <row r="82" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="10" t="n">
+    <row r="82" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="10">
         <v>81</v>
       </c>
       <c r="B82" s="11" t="s">
@@ -5725,8 +5607,8 @@
       <c r="J82" s="10"/>
       <c r="K82" s="10"/>
     </row>
-    <row r="83" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="10" t="n">
+    <row r="83" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="10">
         <v>82</v>
       </c>
       <c r="B83" s="11" t="s">
@@ -5754,8 +5636,8 @@
       <c r="J83" s="10"/>
       <c r="K83" s="10"/>
     </row>
-    <row r="84" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="10" t="n">
+    <row r="84" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="10">
         <v>83</v>
       </c>
       <c r="B84" s="11" t="s">
@@ -5783,8 +5665,8 @@
       <c r="J84" s="10"/>
       <c r="K84" s="10"/>
     </row>
-    <row r="85" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="10" t="n">
+    <row r="85" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="10">
         <v>84</v>
       </c>
       <c r="B85" s="11" t="s">
@@ -5812,8 +5694,8 @@
       <c r="J85" s="10"/>
       <c r="K85" s="10"/>
     </row>
-    <row r="86" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="10" t="n">
+    <row r="86" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="10">
         <v>85</v>
       </c>
       <c r="B86" s="11" t="s">
@@ -5841,8 +5723,8 @@
       <c r="J86" s="10"/>
       <c r="K86" s="10"/>
     </row>
-    <row r="87" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="10" t="n">
+    <row r="87" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="10">
         <v>86</v>
       </c>
       <c r="B87" s="11" t="s">
@@ -5870,8 +5752,8 @@
       <c r="J87" s="10"/>
       <c r="K87" s="10"/>
     </row>
-    <row r="88" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="10" t="n">
+    <row r="88" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="10">
         <v>87</v>
       </c>
       <c r="B88" s="11" t="s">
@@ -5899,8 +5781,8 @@
       <c r="J88" s="10"/>
       <c r="K88" s="10"/>
     </row>
-    <row r="89" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="10" t="n">
+    <row r="89" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="10">
         <v>88</v>
       </c>
       <c r="B89" s="11" t="s">
@@ -5928,8 +5810,8 @@
       <c r="J89" s="10"/>
       <c r="K89" s="10"/>
     </row>
-    <row r="90" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="10" t="n">
+    <row r="90" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="10">
         <v>89</v>
       </c>
       <c r="B90" s="11" t="s">
@@ -5957,8 +5839,8 @@
       <c r="J90" s="10"/>
       <c r="K90" s="10"/>
     </row>
-    <row r="91" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="10" t="n">
+    <row r="91" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="10">
         <v>90</v>
       </c>
       <c r="B91" s="11" t="s">
@@ -5986,8 +5868,8 @@
       <c r="J91" s="10"/>
       <c r="K91" s="10"/>
     </row>
-    <row r="92" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="10" t="n">
+    <row r="92" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="10">
         <v>91</v>
       </c>
       <c r="B92" s="11" t="s">
@@ -6015,8 +5897,8 @@
       <c r="J92" s="10"/>
       <c r="K92" s="10"/>
     </row>
-    <row r="93" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="10" t="n">
+    <row r="93" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="10">
         <v>92</v>
       </c>
       <c r="B93" s="11" t="s">
@@ -6044,8 +5926,8 @@
       <c r="J93" s="10"/>
       <c r="K93" s="10"/>
     </row>
-    <row r="94" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="10" t="n">
+    <row r="94" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="10">
         <v>93</v>
       </c>
       <c r="B94" s="11" t="s">
@@ -6073,8 +5955,8 @@
       <c r="J94" s="10"/>
       <c r="K94" s="10"/>
     </row>
-    <row r="95" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="10" t="n">
+    <row r="95" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="10">
         <v>94</v>
       </c>
       <c r="B95" s="11" t="s">
@@ -6102,8 +5984,8 @@
       <c r="J95" s="10"/>
       <c r="K95" s="10"/>
     </row>
-    <row r="96" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="10" t="n">
+    <row r="96" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="10">
         <v>95</v>
       </c>
       <c r="B96" s="11" t="s">
@@ -6131,8 +6013,8 @@
       <c r="J96" s="10"/>
       <c r="K96" s="10"/>
     </row>
-    <row r="97" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="10" t="n">
+    <row r="97" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="10">
         <v>96</v>
       </c>
       <c r="B97" s="11" t="s">
@@ -6160,8 +6042,8 @@
       <c r="J97" s="10"/>
       <c r="K97" s="10"/>
     </row>
-    <row r="98" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="10" t="n">
+    <row r="98" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="10">
         <v>97</v>
       </c>
       <c r="B98" s="11" t="s">
@@ -6189,8 +6071,8 @@
       <c r="J98" s="10"/>
       <c r="K98" s="10"/>
     </row>
-    <row r="99" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="10" t="n">
+    <row r="99" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="10">
         <v>98</v>
       </c>
       <c r="B99" s="11" t="s">
@@ -6218,8 +6100,8 @@
       <c r="J99" s="10"/>
       <c r="K99" s="10"/>
     </row>
-    <row r="100" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="10" t="n">
+    <row r="100" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="10">
         <v>99</v>
       </c>
       <c r="B100" s="11" t="s">
@@ -6247,8 +6129,8 @@
       <c r="J100" s="10"/>
       <c r="K100" s="10"/>
     </row>
-    <row r="101" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="10" t="n">
+    <row r="101" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="10">
         <v>100</v>
       </c>
       <c r="B101" s="11" t="s">
@@ -6276,8 +6158,8 @@
       <c r="J101" s="10"/>
       <c r="K101" s="10"/>
     </row>
-    <row r="102" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="10" t="n">
+    <row r="102" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="10">
         <v>101</v>
       </c>
       <c r="B102" s="11" t="s">
@@ -6305,8 +6187,8 @@
       <c r="J102" s="10"/>
       <c r="K102" s="10"/>
     </row>
-    <row r="103" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="10" t="n">
+    <row r="103" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="10">
         <v>102</v>
       </c>
       <c r="B103" s="11" t="s">
@@ -6334,8 +6216,8 @@
       <c r="J103" s="10"/>
       <c r="K103" s="10"/>
     </row>
-    <row r="104" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="10" t="n">
+    <row r="104" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="10">
         <v>103</v>
       </c>
       <c r="B104" s="11" t="s">
@@ -6363,8 +6245,8 @@
       <c r="J104" s="10"/>
       <c r="K104" s="10"/>
     </row>
-    <row r="105" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="10" t="n">
+    <row r="105" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="10">
         <v>104</v>
       </c>
       <c r="B105" s="11" t="s">
@@ -6392,8 +6274,8 @@
       <c r="J105" s="10"/>
       <c r="K105" s="10"/>
     </row>
-    <row r="106" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="10" t="n">
+    <row r="106" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="10">
         <v>105</v>
       </c>
       <c r="B106" s="11" t="s">
@@ -6421,8 +6303,8 @@
       <c r="J106" s="10"/>
       <c r="K106" s="10"/>
     </row>
-    <row r="107" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="10" t="n">
+    <row r="107" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="10">
         <v>106</v>
       </c>
       <c r="B107" s="11" t="s">
@@ -6450,8 +6332,8 @@
       <c r="J107" s="10"/>
       <c r="K107" s="10"/>
     </row>
-    <row r="108" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="10" t="n">
+    <row r="108" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="10">
         <v>107</v>
       </c>
       <c r="B108" s="11" t="s">
@@ -6479,8 +6361,8 @@
       <c r="J108" s="10"/>
       <c r="K108" s="10"/>
     </row>
-    <row r="109" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="10" t="n">
+    <row r="109" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="10">
         <v>108</v>
       </c>
       <c r="B109" s="11" t="s">
@@ -6508,8 +6390,8 @@
       <c r="J109" s="10"/>
       <c r="K109" s="10"/>
     </row>
-    <row r="110" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="10" t="n">
+    <row r="110" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="10">
         <v>109</v>
       </c>
       <c r="B110" s="11" t="s">
@@ -6537,8 +6419,8 @@
       <c r="J110" s="10"/>
       <c r="K110" s="10"/>
     </row>
-    <row r="111" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="10" t="n">
+    <row r="111" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="10">
         <v>110</v>
       </c>
       <c r="B111" s="11" t="s">
@@ -6566,8 +6448,8 @@
       <c r="J111" s="10"/>
       <c r="K111" s="10"/>
     </row>
-    <row r="112" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="10" t="n">
+    <row r="112" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="10">
         <v>111</v>
       </c>
       <c r="B112" s="11" t="s">
@@ -6595,8 +6477,8 @@
       <c r="J112" s="10"/>
       <c r="K112" s="10"/>
     </row>
-    <row r="113" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="10" t="n">
+    <row r="113" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="10">
         <v>112</v>
       </c>
       <c r="B113" s="11" t="s">
@@ -6624,8 +6506,8 @@
       <c r="J113" s="10"/>
       <c r="K113" s="10"/>
     </row>
-    <row r="114" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="10" t="n">
+    <row r="114" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="10">
         <v>113</v>
       </c>
       <c r="B114" s="11" t="s">
@@ -6653,8 +6535,8 @@
       <c r="J114" s="10"/>
       <c r="K114" s="10"/>
     </row>
-    <row r="115" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="10" t="n">
+    <row r="115" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="10">
         <v>114</v>
       </c>
       <c r="B115" s="11" t="s">
@@ -6682,8 +6564,8 @@
       <c r="J115" s="10"/>
       <c r="K115" s="10"/>
     </row>
-    <row r="116" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="10" t="n">
+    <row r="116" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="10">
         <v>115</v>
       </c>
       <c r="B116" s="11" t="s">
@@ -6711,8 +6593,8 @@
       <c r="J116" s="10"/>
       <c r="K116" s="10"/>
     </row>
-    <row r="117" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="10" t="n">
+    <row r="117" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="10">
         <v>116</v>
       </c>
       <c r="B117" s="11" t="s">
@@ -6740,8 +6622,8 @@
       <c r="J117" s="10"/>
       <c r="K117" s="10"/>
     </row>
-    <row r="118" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="10" t="n">
+    <row r="118" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="10">
         <v>117</v>
       </c>
       <c r="B118" s="11" t="s">
@@ -6769,8 +6651,8 @@
       <c r="J118" s="10"/>
       <c r="K118" s="10"/>
     </row>
-    <row r="119" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="10" t="n">
+    <row r="119" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="10">
         <v>118</v>
       </c>
       <c r="B119" s="11" t="s">
@@ -6798,8 +6680,8 @@
       <c r="J119" s="10"/>
       <c r="K119" s="10"/>
     </row>
-    <row r="120" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="10" t="n">
+    <row r="120" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A120" s="10">
         <v>119</v>
       </c>
       <c r="B120" s="11" t="s">
@@ -6827,8 +6709,8 @@
       <c r="J120" s="10"/>
       <c r="K120" s="10"/>
     </row>
-    <row r="121" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="10" t="n">
+    <row r="121" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="10">
         <v>120</v>
       </c>
       <c r="B121" s="11" t="s">
@@ -6856,8 +6738,8 @@
       <c r="J121" s="10"/>
       <c r="K121" s="10"/>
     </row>
-    <row r="122" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="10" t="n">
+    <row r="122" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A122" s="10">
         <v>121</v>
       </c>
       <c r="B122" s="11" t="s">
@@ -6885,8 +6767,8 @@
       <c r="J122" s="10"/>
       <c r="K122" s="10"/>
     </row>
-    <row r="123" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="10" t="n">
+    <row r="123" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="10">
         <v>122</v>
       </c>
       <c r="B123" s="11" t="s">
@@ -6914,8 +6796,8 @@
       <c r="J123" s="10"/>
       <c r="K123" s="10"/>
     </row>
-    <row r="124" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="10" t="n">
+    <row r="124" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="10">
         <v>123</v>
       </c>
       <c r="B124" s="11" t="s">
@@ -6943,8 +6825,8 @@
       <c r="J124" s="10"/>
       <c r="K124" s="10"/>
     </row>
-    <row r="125" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="10" t="n">
+    <row r="125" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="10">
         <v>124</v>
       </c>
       <c r="B125" s="11" t="s">
@@ -6972,8 +6854,8 @@
       <c r="J125" s="10"/>
       <c r="K125" s="10"/>
     </row>
-    <row r="126" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="10" t="n">
+    <row r="126" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="10">
         <v>125</v>
       </c>
       <c r="B126" s="11" t="s">
@@ -7001,8 +6883,8 @@
       <c r="J126" s="10"/>
       <c r="K126" s="10"/>
     </row>
-    <row r="127" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="10" t="n">
+    <row r="127" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="10">
         <v>126</v>
       </c>
       <c r="B127" s="11" t="s">
@@ -7031,43 +6913,37 @@
       <c r="K127" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K127"/>
+  <autoFilter ref="A1:K127" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <conditionalFormatting sqref="G2:G127">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+      <formula>"High"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H2:H127">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"Not Tested"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G127">
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
-      <formula>"High"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" error="Please choose a value from the list." errorStyle="stop" errorTitle="Invalid entry" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H127" type="list">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." sqref="H2:H127" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Not Tested,Pass,Fail,Blocked,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G127" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G127" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/dc-uat-checklist-updated.xlsx
+++ b/dc-uat-checklist-updated.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\daycare-system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AEAC74A-89F9-4C54-81C0-14457124E693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5851DC6-6DF7-4DEC-A303-AF0E4799F91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="573">
   <si>
     <t>Emagine U At Play — UAT Checklist</t>
   </si>
@@ -1802,6 +1802,12 @@
   </si>
   <si>
     <t>Child View Needed</t>
+  </si>
+  <si>
+    <t>authorized for pickup - not showing</t>
+  </si>
+  <si>
+    <t>is_primary=true not marked in parent list</t>
   </si>
 </sst>
 </file>
@@ -2530,11 +2536,11 @@
       </c>
       <c r="D9" s="6">
         <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B9,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E9" s="6">
         <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B9,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F9" s="6">
         <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B9,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
@@ -2550,7 +2556,7 @@
       </c>
       <c r="I9" s="7">
         <f t="shared" si="0"/>
-        <v>0.375</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
@@ -2596,11 +2602,11 @@
       </c>
       <c r="D11" s="6">
         <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B11,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="6">
         <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B11,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6">
         <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B11,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
@@ -2616,7 +2622,7 @@
       </c>
       <c r="I11" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.35">
@@ -3157,11 +3163,11 @@
       </c>
       <c r="D28" s="8">
         <f t="shared" si="1"/>
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E28" s="8">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F28" s="8">
         <f t="shared" si="1"/>
@@ -3177,7 +3183,7 @@
       </c>
       <c r="I28" s="9">
         <f t="shared" si="0"/>
-        <v>0.15873015873015872</v>
+        <v>0.20634920634920634</v>
       </c>
     </row>
   </sheetData>
@@ -3919,7 +3925,7 @@
         <v>77</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I24" s="11"/>
       <c r="J24" s="10"/>
@@ -3948,7 +3954,7 @@
         <v>77</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I25" s="11"/>
       <c r="J25" s="10"/>
@@ -3977,7 +3983,7 @@
         <v>68</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I26" s="11"/>
       <c r="J26" s="10"/>
@@ -4006,7 +4012,7 @@
         <v>68</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I27" s="11"/>
       <c r="J27" s="10"/>
@@ -4035,7 +4041,7 @@
         <v>77</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I28" s="11"/>
       <c r="J28" s="10"/>
@@ -4124,7 +4130,9 @@
       <c r="H31" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I31" s="11"/>
+      <c r="I31" s="11" t="s">
+        <v>571</v>
+      </c>
       <c r="J31" s="10"/>
       <c r="K31" s="10"/>
     </row>
@@ -4153,7 +4161,9 @@
       <c r="H32" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I32" s="11"/>
+      <c r="I32" s="11" t="s">
+        <v>572</v>
+      </c>
       <c r="J32" s="10"/>
       <c r="K32" s="10"/>
     </row>
@@ -4180,7 +4190,7 @@
         <v>77</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I33" s="11"/>
       <c r="J33" s="10"/>

--- a/dc-uat-checklist-updated.xlsx
+++ b/dc-uat-checklist-updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\daycare-system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5851DC6-6DF7-4DEC-A303-AF0E4799F91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25FA82F-0E9A-4002-B920-2EC631FA5D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="576">
   <si>
     <t>Emagine U At Play — UAT Checklist</t>
   </si>
@@ -1808,6 +1808,15 @@
   </si>
   <si>
     <t>is_primary=true not marked in parent list</t>
+  </si>
+  <si>
+    <t>It checks enrollment start date, not the child age on today -  I think it is ok.</t>
+  </si>
+  <si>
+    <t>It is not allowing to enroll which is right.</t>
+  </si>
+  <si>
+    <t>Only Pending and Active status are there.</t>
   </si>
 </sst>
 </file>
@@ -2602,15 +2611,15 @@
       </c>
       <c r="D11" s="6">
         <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B11,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11" s="6">
         <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B11,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" s="6">
         <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B11,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="6">
         <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B11,'UAT Checklist'!$H$2:$H$127,"Blocked")</f>
@@ -2618,11 +2627,11 @@
       </c>
       <c r="H11" s="6">
         <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B11,'UAT Checklist'!$H$2:$H$127,"N/A")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.35">
@@ -2635,11 +2644,11 @@
       </c>
       <c r="D12" s="6">
         <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B12,'UAT Checklist'!$H$2:$H$127,"Not Tested")</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E12" s="6">
         <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B12,'UAT Checklist'!$H$2:$H$127,"Pass")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F12" s="6">
         <f>COUNTIFS('UAT Checklist'!$B$2:$B$127,$B12,'UAT Checklist'!$H$2:$H$127,"Fail")</f>
@@ -2655,7 +2664,7 @@
       </c>
       <c r="I12" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.35">
@@ -3163,15 +3172,15 @@
       </c>
       <c r="D28" s="8">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E28" s="8">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F28" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="8">
         <f t="shared" si="1"/>
@@ -3179,11 +3188,11 @@
       </c>
       <c r="H28" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="9">
         <f t="shared" si="0"/>
-        <v>0.20634920634920634</v>
+        <v>0.26984126984126983</v>
       </c>
     </row>
   </sheetData>
@@ -4219,7 +4228,7 @@
         <v>77</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I34" s="11"/>
       <c r="J34" s="10"/>
@@ -4248,7 +4257,7 @@
         <v>77</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I35" s="11"/>
       <c r="J35" s="10"/>
@@ -4277,7 +4286,7 @@
         <v>77</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I36" s="11"/>
       <c r="J36" s="10"/>
@@ -4306,7 +4315,7 @@
         <v>68</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I37" s="11"/>
       <c r="J37" s="10"/>
@@ -4335,7 +4344,7 @@
         <v>68</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I38" s="11"/>
       <c r="J38" s="10"/>
@@ -4364,9 +4373,11 @@
         <v>68</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I39" s="11"/>
+        <v>26</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>573</v>
+      </c>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
     </row>
@@ -4393,9 +4404,11 @@
         <v>68</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I40" s="11"/>
+        <v>26</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>574</v>
+      </c>
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
     </row>
@@ -4422,9 +4435,11 @@
         <v>77</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I41" s="11"/>
+        <v>26</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>575</v>
+      </c>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
     </row>
@@ -4451,7 +4466,7 @@
         <v>77</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I42" s="11"/>
       <c r="J42" s="10"/>
@@ -4480,7 +4495,7 @@
         <v>142</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I43" s="11"/>
       <c r="J43" s="10"/>

--- a/dc-uat-checklist-updated.xlsx
+++ b/dc-uat-checklist-updated.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>Remaining = 2 (4 included − 2 completed), computed live. Tested by linking sessions directly in DB — UI cannot link sessions to a package (see PKG-07).</t>
+          <t>Remaining = 2 (4 included − 2 completed), computed live. Retested with sessions booked from the package on the session form and marked completed.</t>
         </is>
       </c>
       <c r="J90" s="10" t="n"/>
@@ -5709,12 +5709,12 @@
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>Not implemented: the therapy session form has no "from package" option and nothing sets therapy_sessions.child_therapy_package_id. As a result package balances never decrease through the UI.</t>
+          <t>Retested after fix: Therapy Sessions &gt; New/Edit now has a Payment field — "Use package — oldest first", a specific package (shows "x of y left"), or "Pay per session". Session saves with child_therapy_package_id set to that package. Rejected with a message: another child's package, cancelled or expired package, package that doesn't cover the therapy, or no sessions left. Session page shows Payment = package.</t>
         </is>
       </c>
       <c r="J91" s="10" t="n"/>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>Completed package-linked sessions are excluded from the billable/unbilled list (sessions linked via DB — see PKG-07).</t>
+          <t>Completed sessions booked from a package are excluded from the billable/unbilled list on Create Invoice (retested with sessions booked from the package in the UI).</t>
         </is>
       </c>
       <c r="J92" s="10" t="n"/>
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
-          <t>Depends on PKG-07: sessions cannot be booked from a package, so there is no package allocation (FIFO or otherwise) to test.</t>
+          <t>Retested after fix: child with two active OT packages — "Use package — oldest first" drew sessions from the older package (earlier purchased_at) until its balance was used, then moved to the newer one. Scheduled sessions reserve a slot; cancelled / no-show give it back.</t>
         </is>
       </c>
       <c r="J94" s="10" t="n"/>
@@ -5948,12 +5948,12 @@
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
-          <t>Not implemented: purchase form shows no info panel with the child's existing unused sessions before the price is set.</t>
+          <t>Retested after fix: Purchase Package form now shows an "Existing Balance" panel as soon as the child is picked (before the price is set): each active package with sessions left, purchase/expiry date, invoice no. and per-therapy "x of y left" (booked sessions noted). A child with none shows "OK to buy a new one".</t>
         </is>
       </c>
       <c r="J96" s="10" t="n"/>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>Status → cancelled. (Booking from a package is not built — PKG-07 — so "no longer offers balance" cannot be exercised.)</t>
+          <t>Status → cancelled, and the cancelled package is no longer offered on the session form (booking it directly is rejected).</t>
         </is>
       </c>
       <c r="J97" s="10" t="n"/>
@@ -6043,12 +6043,12 @@
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
         <is>
-          <t>Staff can purchase/cancel child packages (controller only blocks parents). Staff: template create 403, purchase 302 (SAVED), cancel 302 (CANCELLED); Parent: view own 200, other child n/a, purchase 403.</t>
+          <t>Agreed rule (product owner): staff may buy a package for a child and cancel it, but cannot create/edit package templates — Package Catalog create returns 403 for staff. Parent: read-only, own child only, cannot purchase/cancel (403). Retested: staff template create 403, staff purchase OK (with invoice), parent purchase 403.</t>
         </is>
       </c>
       <c r="J98" s="10" t="n"/>
@@ -6280,12 +6280,12 @@
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>Partly: buying a package on Create Invoice creates exactly one invoice item with child_therapy_package_id set; but buying via Therapy Packages → Purchase creates NO invoice item (3 package(s) for this child have no invoice).</t>
+          <t>Retested after fix: Child Packages &gt; Purchase now creates one draft invoice (due in 7 days) for the child's primary parent with exactly one item for the purchase price, child_therapy_package_id set; the package is linked to that invoice. Buying a package on Create Invoice still gives one item. A ৳0 package or a child with no parent is saved without an invoice and the user is told.</t>
         </is>
       </c>
       <c r="J103" s="10" t="n"/>
